--- a/database/event/7148/event_7148_evp_summary.xlsx
+++ b/database/event/7148/event_7148_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>9.7569</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>5.6498</v>
       </c>
       <c r="D2" t="n">
         <v>3.5202</v>
@@ -545,7 +545,7 @@
         <v>7.516</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>4.3522</v>
       </c>
       <c r="D3" t="n">
         <v>2.6149</v>
@@ -591,7 +591,7 @@
         <v>6.5816</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>3.8111</v>
       </c>
       <c r="D4" t="n">
         <v>2.2375</v>
@@ -637,7 +637,7 @@
         <v>6.1641</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>3.5694</v>
       </c>
       <c r="D5" t="n">
         <v>2.0688</v>
@@ -683,7 +683,7 @@
         <v>5.7198</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>3.3121</v>
       </c>
       <c r="D6" t="n">
         <v>1.8893</v>
@@ -729,7 +729,7 @@
         <v>4.3906</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>2.5424</v>
       </c>
       <c r="D7" t="n">
         <v>1.3523</v>
@@ -775,7 +775,7 @@
         <v>4.3741</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>2.5329</v>
       </c>
       <c r="D8" t="n">
         <v>1.3457</v>
@@ -821,7 +821,7 @@
         <v>4.1797</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>2.4203</v>
       </c>
       <c r="D9" t="n">
         <v>1.2671</v>
@@ -867,7 +867,7 @@
         <v>3.918</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>2.2688</v>
       </c>
       <c r="D10" t="n">
         <v>1.1614</v>
@@ -913,7 +913,7 @@
         <v>3.5662</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>2.065</v>
       </c>
       <c r="D11" t="n">
         <v>1.0193</v>
@@ -959,7 +959,7 @@
         <v>3.085</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1.7864</v>
       </c>
       <c r="D12" t="n">
         <v>0.8249</v>
@@ -1005,7 +1005,7 @@
         <v>3.0362</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1.7581</v>
       </c>
       <c r="D13" t="n">
         <v>0.8052</v>
@@ -1051,7 +1051,7 @@
         <v>2.8308</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1.6392</v>
       </c>
       <c r="D14" t="n">
         <v>0.7222</v>
@@ -1097,7 +1097,7 @@
         <v>2.8256</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1.6362</v>
       </c>
       <c r="D15" t="n">
         <v>0.7201</v>
@@ -1143,7 +1143,7 @@
         <v>2.7305</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1.5811</v>
       </c>
       <c r="D16" t="n">
         <v>0.6817</v>
@@ -1189,7 +1189,7 @@
         <v>2.6544</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1.5371</v>
       </c>
       <c r="D17" t="n">
         <v>0.651</v>
@@ -1235,7 +1235,7 @@
         <v>2.6335</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1.525</v>
       </c>
       <c r="D18" t="n">
         <v>0.6425</v>
@@ -1281,7 +1281,7 @@
         <v>2.2901</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1.3261</v>
       </c>
       <c r="D19" t="n">
         <v>0.5038</v>
@@ -1327,7 +1327,7 @@
         <v>2.2083</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1.2787</v>
       </c>
       <c r="D20" t="n">
         <v>0.4707</v>
@@ -1373,7 +1373,7 @@
         <v>2.1155</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1.225</v>
       </c>
       <c r="D21" t="n">
         <v>0.4333</v>
@@ -1419,7 +1419,7 @@
         <v>2.0885</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1.2094</v>
       </c>
       <c r="D22" t="n">
         <v>0.4223</v>
@@ -1465,7 +1465,7 @@
         <v>1.8873</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1.0929</v>
       </c>
       <c r="D23" t="n">
         <v>0.3411</v>
@@ -1511,7 +1511,7 @@
         <v>1.8506</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1.0716</v>
       </c>
       <c r="D24" t="n">
         <v>0.3262</v>
@@ -1557,7 +1557,7 @@
         <v>1.8498</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1.0711</v>
       </c>
       <c r="D25" t="n">
         <v>0.3259</v>
@@ -1603,7 +1603,7 @@
         <v>1.7974</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1.0408</v>
       </c>
       <c r="D26" t="n">
         <v>0.3047</v>
@@ -1649,7 +1649,7 @@
         <v>1.7923</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>1.0378</v>
       </c>
       <c r="D27" t="n">
         <v>0.3027</v>
@@ -1695,7 +1695,7 @@
         <v>1.4891</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.8623</v>
       </c>
       <c r="D28" t="n">
         <v>0.1802</v>
@@ -1741,7 +1741,7 @@
         <v>1.3185</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.7635</v>
       </c>
       <c r="D29" t="n">
         <v>0.1113</v>
@@ -1787,7 +1787,7 @@
         <v>1.181</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.6839</v>
       </c>
       <c r="D30" t="n">
         <v>0.0557</v>
@@ -1833,7 +1833,7 @@
         <v>1.1304</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.6546</v>
       </c>
       <c r="D31" t="n">
         <v>0.0353</v>
@@ -1879,7 +1879,7 @@
         <v>1.1104</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>0.643</v>
       </c>
       <c r="D32" t="n">
         <v>0.0272</v>
@@ -1925,7 +1925,7 @@
         <v>1.1085</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.6419</v>
       </c>
       <c r="D33" t="n">
         <v>0.0264</v>
@@ -1971,7 +1971,7 @@
         <v>1.0396</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.602</v>
       </c>
       <c r="D34" t="n">
         <v>-0.0014</v>
@@ -2017,7 +2017,7 @@
         <v>0.9396</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.5441</v>
       </c>
       <c r="D35" t="n">
         <v>-0.0418</v>
@@ -2063,7 +2063,7 @@
         <v>0.8424</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.4878</v>
       </c>
       <c r="D36" t="n">
         <v>-0.08110000000000001</v>
@@ -2109,7 +2109,7 @@
         <v>0.8167</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.4729</v>
       </c>
       <c r="D37" t="n">
         <v>-0.0914</v>
@@ -2155,7 +2155,7 @@
         <v>0.7231</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.4187</v>
       </c>
       <c r="D38" t="n">
         <v>-0.1292</v>
@@ -2201,7 +2201,7 @@
         <v>0.7121</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.4123</v>
       </c>
       <c r="D39" t="n">
         <v>-0.1337</v>
@@ -2247,7 +2247,7 @@
         <v>0.6515</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.3773</v>
       </c>
       <c r="D40" t="n">
         <v>-0.1582</v>
@@ -2293,7 +2293,7 @@
         <v>0.6385</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>0.3697</v>
       </c>
       <c r="D41" t="n">
         <v>-0.1634</v>
@@ -2339,7 +2339,7 @@
         <v>0.4128</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>0.239</v>
       </c>
       <c r="D42" t="n">
         <v>-0.2546</v>
@@ -2385,7 +2385,7 @@
         <v>0.3198</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>0.1852</v>
       </c>
       <c r="D43" t="n">
         <v>-0.2922</v>
@@ -2431,7 +2431,7 @@
         <v>0.2596</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.1503</v>
       </c>
       <c r="D44" t="n">
         <v>-0.3165</v>
@@ -2477,7 +2477,7 @@
         <v>0.256</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>0.1482</v>
       </c>
       <c r="D45" t="n">
         <v>-0.3179</v>
@@ -2523,7 +2523,7 @@
         <v>0.2316</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>0.1341</v>
       </c>
       <c r="D46" t="n">
         <v>-0.3278</v>
@@ -2569,7 +2569,7 @@
         <v>0.1962</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>0.1136</v>
       </c>
       <c r="D47" t="n">
         <v>-0.3421</v>
@@ -2615,7 +2615,7 @@
         <v>0.1864</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>0.1079</v>
       </c>
       <c r="D48" t="n">
         <v>-0.3461</v>
@@ -2661,7 +2661,7 @@
         <v>0.0863</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="D49" t="n">
         <v>-0.3865</v>
@@ -2707,7 +2707,7 @@
         <v>0.0294</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="D50" t="n">
         <v>-0.4095</v>
@@ -2753,7 +2753,7 @@
         <v>-0.0146</v>
       </c>
       <c r="C51" t="n">
-        <v>-0</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="D51" t="n">
         <v>-0.4273</v>
@@ -2799,7 +2799,7 @@
         <v>-0.0989</v>
       </c>
       <c r="C52" t="n">
-        <v>-0</v>
+        <v>-0.0573</v>
       </c>
       <c r="D52" t="n">
         <v>-0.4613</v>
@@ -2845,7 +2845,7 @@
         <v>-0.1346</v>
       </c>
       <c r="C53" t="n">
-        <v>-0</v>
+        <v>-0.0779</v>
       </c>
       <c r="D53" t="n">
         <v>-0.4757</v>
@@ -2891,7 +2891,7 @@
         <v>-0.137</v>
       </c>
       <c r="C54" t="n">
-        <v>-0</v>
+        <v>-0.0793</v>
       </c>
       <c r="D54" t="n">
         <v>-0.4767</v>
@@ -2937,7 +2937,7 @@
         <v>-0.1385</v>
       </c>
       <c r="C55" t="n">
-        <v>-0</v>
+        <v>-0.08019999999999999</v>
       </c>
       <c r="D55" t="n">
         <v>-0.4773</v>
@@ -2983,7 +2983,7 @@
         <v>-0.1857</v>
       </c>
       <c r="C56" t="n">
-        <v>-0</v>
+        <v>-0.1075</v>
       </c>
       <c r="D56" t="n">
         <v>-0.4964</v>
@@ -3029,7 +3029,7 @@
         <v>-0.3216</v>
       </c>
       <c r="C57" t="n">
-        <v>-0</v>
+        <v>-0.1862</v>
       </c>
       <c r="D57" t="n">
         <v>-0.5513</v>
@@ -3075,7 +3075,7 @@
         <v>-0.3338</v>
       </c>
       <c r="C58" t="n">
-        <v>-0</v>
+        <v>-0.1933</v>
       </c>
       <c r="D58" t="n">
         <v>-0.5562</v>
@@ -3121,7 +3121,7 @@
         <v>-0.3367</v>
       </c>
       <c r="C59" t="n">
-        <v>-0</v>
+        <v>-0.195</v>
       </c>
       <c r="D59" t="n">
         <v>-0.5574</v>
@@ -3167,7 +3167,7 @@
         <v>-0.4014</v>
       </c>
       <c r="C60" t="n">
-        <v>-0</v>
+        <v>-0.2324</v>
       </c>
       <c r="D60" t="n">
         <v>-0.5835</v>
@@ -3213,7 +3213,7 @@
         <v>-0.4269</v>
       </c>
       <c r="C61" t="n">
-        <v>-0</v>
+        <v>-0.2472</v>
       </c>
       <c r="D61" t="n">
         <v>-0.5938</v>
@@ -3259,7 +3259,7 @@
         <v>-0.4563</v>
       </c>
       <c r="C62" t="n">
-        <v>-0</v>
+        <v>-0.2642</v>
       </c>
       <c r="D62" t="n">
         <v>-0.6057</v>
@@ -3305,7 +3305,7 @@
         <v>-0.4753</v>
       </c>
       <c r="C63" t="n">
-        <v>-0</v>
+        <v>-0.2752</v>
       </c>
       <c r="D63" t="n">
         <v>-0.6133999999999999</v>
@@ -3351,7 +3351,7 @@
         <v>-0.5441</v>
       </c>
       <c r="C64" t="n">
-        <v>-0</v>
+        <v>-0.3151</v>
       </c>
       <c r="D64" t="n">
         <v>-0.6412</v>
@@ -3397,7 +3397,7 @@
         <v>-0.835</v>
       </c>
       <c r="C65" t="n">
-        <v>-0</v>
+        <v>-0.4835</v>
       </c>
       <c r="D65" t="n">
         <v>-0.7587</v>
@@ -3443,7 +3443,7 @@
         <v>-1.0561</v>
       </c>
       <c r="C66" t="n">
-        <v>-0</v>
+        <v>-0.6115</v>
       </c>
       <c r="D66" t="n">
         <v>-0.848</v>
@@ -3489,7 +3489,7 @@
         <v>-1.1941</v>
       </c>
       <c r="C67" t="n">
-        <v>-0</v>
+        <v>-0.6915</v>
       </c>
       <c r="D67" t="n">
         <v>-0.9038</v>
@@ -3535,7 +3535,7 @@
         <v>-1.1943</v>
       </c>
       <c r="C68" t="n">
-        <v>-0</v>
+        <v>-0.6916</v>
       </c>
       <c r="D68" t="n">
         <v>-0.9038</v>
@@ -3581,7 +3581,7 @@
         <v>-1.2336</v>
       </c>
       <c r="C69" t="n">
-        <v>-0</v>
+        <v>-0.7143</v>
       </c>
       <c r="D69" t="n">
         <v>-0.9197</v>
@@ -3627,7 +3627,7 @@
         <v>-1.3642</v>
       </c>
       <c r="C70" t="n">
-        <v>-0</v>
+        <v>-0.79</v>
       </c>
       <c r="D70" t="n">
         <v>-0.9725</v>
@@ -3673,7 +3673,7 @@
         <v>-1.3847</v>
       </c>
       <c r="C71" t="n">
-        <v>-0</v>
+        <v>-0.8018</v>
       </c>
       <c r="D71" t="n">
         <v>-0.9808</v>
@@ -3719,7 +3719,7 @@
         <v>-1.5213</v>
       </c>
       <c r="C72" t="n">
-        <v>-0</v>
+        <v>-0.8809</v>
       </c>
       <c r="D72" t="n">
         <v>-1.0359</v>
@@ -3765,7 +3765,7 @@
         <v>-1.568</v>
       </c>
       <c r="C73" t="n">
-        <v>-0</v>
+        <v>-0.908</v>
       </c>
       <c r="D73" t="n">
         <v>-1.0548</v>
@@ -3811,7 +3811,7 @@
         <v>-2.2599</v>
       </c>
       <c r="C74" t="n">
-        <v>-0</v>
+        <v>-1.3086</v>
       </c>
       <c r="D74" t="n">
         <v>-1.3343</v>
@@ -3857,7 +3857,7 @@
         <v>-2.2961</v>
       </c>
       <c r="C75" t="n">
-        <v>-0</v>
+        <v>-1.3296</v>
       </c>
       <c r="D75" t="n">
         <v>-1.3489</v>
@@ -3903,7 +3903,7 @@
         <v>-2.3129</v>
       </c>
       <c r="C76" t="n">
-        <v>-0</v>
+        <v>-1.3393</v>
       </c>
       <c r="D76" t="n">
         <v>-1.3557</v>
@@ -3949,7 +3949,7 @@
         <v>-2.4339</v>
       </c>
       <c r="C77" t="n">
-        <v>-0</v>
+        <v>-1.4094</v>
       </c>
       <c r="D77" t="n">
         <v>-1.4046</v>
@@ -3995,7 +3995,7 @@
         <v>-2.7111</v>
       </c>
       <c r="C78" t="n">
-        <v>-0</v>
+        <v>-1.5699</v>
       </c>
       <c r="D78" t="n">
         <v>-1.5166</v>
@@ -4041,7 +4041,7 @@
         <v>-3.1997</v>
       </c>
       <c r="C79" t="n">
-        <v>-0</v>
+        <v>-1.8528</v>
       </c>
       <c r="D79" t="n">
         <v>-1.714</v>
@@ -4087,7 +4087,7 @@
         <v>-5.2374</v>
       </c>
       <c r="C80" t="n">
-        <v>-0</v>
+        <v>-3.0328</v>
       </c>
       <c r="D80" t="n">
         <v>-2.5372</v>
@@ -4133,7 +4133,7 @@
         <v>-5.2599</v>
       </c>
       <c r="C81" t="n">
-        <v>-0</v>
+        <v>-3.0458</v>
       </c>
       <c r="D81" t="n">
         <v>-2.5462</v>

--- a/database/event/7148/event_7148_evp_summary.xlsx
+++ b/database/event/7148/event_7148_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.7569</v>
+        <v>10.1656</v>
       </c>
       <c r="C2" t="n">
-        <v>5.6498</v>
+        <v>5.8865</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5202</v>
+        <v>3.6061</v>
       </c>
       <c r="E2" t="n">
-        <v>9.7569</v>
+        <v>10.1656</v>
       </c>
       <c r="F2" t="n">
-        <v>3.8285</v>
+        <v>4.2372</v>
       </c>
       <c r="G2" t="n">
         <v>5.9284</v>
       </c>
       <c r="H2" t="n">
-        <v>3.8285</v>
+        <v>4.3408</v>
       </c>
       <c r="I2" t="n">
-        <v>3.8642</v>
+        <v>4.4142</v>
       </c>
       <c r="J2" t="n">
         <v>5.9284</v>
@@ -529,7 +529,7 @@
         <v>177</v>
       </c>
       <c r="M2" t="n">
-        <v>9.7926</v>
+        <v>10.3426</v>
       </c>
       <c r="N2" t="n">
         <v>404</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.516</v>
+        <v>8.0517</v>
       </c>
       <c r="C3" t="n">
-        <v>4.3522</v>
+        <v>4.6624</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6149</v>
+        <v>2.7639</v>
       </c>
       <c r="E3" t="n">
-        <v>7.516</v>
+        <v>8.0517</v>
       </c>
       <c r="F3" t="n">
-        <v>4.2125</v>
+        <v>4.7482</v>
       </c>
       <c r="G3" t="n">
         <v>3.3035</v>
       </c>
       <c r="H3" t="n">
-        <v>4.3022</v>
+        <v>5.1422</v>
       </c>
       <c r="I3" t="n">
-        <v>4.3222</v>
+        <v>5.1855</v>
       </c>
       <c r="J3" t="n">
         <v>3.3035</v>
@@ -575,7 +575,7 @@
         <v>114</v>
       </c>
       <c r="M3" t="n">
-        <v>7.6257</v>
+        <v>8.489000000000001</v>
       </c>
       <c r="N3" t="n">
         <v>314</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.5816</v>
+        <v>6.9695</v>
       </c>
       <c r="C4" t="n">
-        <v>3.8111</v>
+        <v>4.0358</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2375</v>
+        <v>2.3327</v>
       </c>
       <c r="E4" t="n">
-        <v>6.5816</v>
+        <v>6.9695</v>
       </c>
       <c r="F4" t="n">
-        <v>3.1183</v>
+        <v>3.5062</v>
       </c>
       <c r="G4" t="n">
         <v>3.4633</v>
       </c>
       <c r="H4" t="n">
-        <v>3.1183</v>
+        <v>3.5062</v>
       </c>
       <c r="I4" t="n">
-        <v>3.1474</v>
+        <v>3.5655</v>
       </c>
       <c r="J4" t="n">
         <v>3.4633</v>
@@ -621,7 +621,7 @@
         <v>177</v>
       </c>
       <c r="M4" t="n">
-        <v>6.6107</v>
+        <v>7.0288</v>
       </c>
       <c r="N4" t="n">
         <v>404</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.1641</v>
+        <v>6.1602</v>
       </c>
       <c r="C5" t="n">
-        <v>3.5694</v>
+        <v>3.5671</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0688</v>
+        <v>2.0103</v>
       </c>
       <c r="E5" t="n">
-        <v>6.1641</v>
+        <v>6.1602</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0524</v>
+        <v>1.0485</v>
       </c>
       <c r="G5" t="n">
         <v>5.1117</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0524</v>
+        <v>1.0485</v>
       </c>
       <c r="I5" t="n">
         <v>1.0573</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.7198</v>
+        <v>5.8401</v>
       </c>
       <c r="C6" t="n">
-        <v>3.3121</v>
+        <v>3.3818</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8893</v>
+        <v>1.8828</v>
       </c>
       <c r="E6" t="n">
-        <v>5.7198</v>
+        <v>5.8401</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4938</v>
+        <v>2.6142</v>
       </c>
       <c r="G6" t="n">
         <v>3.2259</v>
       </c>
       <c r="H6" t="n">
-        <v>2.4938</v>
+        <v>2.6142</v>
       </c>
       <c r="I6" t="n">
-        <v>2.5171</v>
+        <v>2.6584</v>
       </c>
       <c r="J6" t="n">
         <v>3.2259</v>
@@ -713,7 +713,7 @@
         <v>177</v>
       </c>
       <c r="M6" t="n">
-        <v>5.743</v>
+        <v>5.8843</v>
       </c>
       <c r="N6" t="n">
         <v>404</v>
@@ -722,219 +722,219 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>donk</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.3906</v>
+        <v>5.4073</v>
       </c>
       <c r="C7" t="n">
-        <v>2.5424</v>
+        <v>3.1311</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3523</v>
+        <v>1.7104</v>
       </c>
       <c r="E7" t="n">
-        <v>4.3906</v>
+        <v>5.4073</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2898</v>
+        <v>3.9118</v>
       </c>
       <c r="G7" t="n">
-        <v>2.1008</v>
+        <v>1.4955</v>
       </c>
       <c r="H7" t="n">
-        <v>2.2898</v>
+        <v>3.9118</v>
       </c>
       <c r="I7" t="n">
-        <v>2.2898</v>
+        <v>3.9118</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1008</v>
+        <v>1.4955</v>
       </c>
       <c r="K7" t="n">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="L7" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="M7" t="n">
-        <v>4.3906</v>
+        <v>5.4073</v>
       </c>
       <c r="N7" t="n">
-        <v>240</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>donk</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.3741</v>
+        <v>4.7563</v>
       </c>
       <c r="C8" t="n">
-        <v>2.5329</v>
+        <v>2.7542</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3457</v>
+        <v>1.451</v>
       </c>
       <c r="E8" t="n">
-        <v>4.3741</v>
+        <v>4.7563</v>
       </c>
       <c r="F8" t="n">
-        <v>2.8786</v>
+        <v>3.0011</v>
       </c>
       <c r="G8" t="n">
-        <v>1.4955</v>
+        <v>1.7552</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8786</v>
+        <v>3.0011</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8786</v>
+        <v>3.0264</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4955</v>
+        <v>1.7552</v>
       </c>
       <c r="K8" t="n">
-        <v>106</v>
+        <v>158</v>
       </c>
       <c r="L8" t="n">
-        <v>85</v>
+        <v>197</v>
       </c>
       <c r="M8" t="n">
-        <v>4.3741</v>
+        <v>4.7816</v>
       </c>
       <c r="N8" t="n">
-        <v>191</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>biguzera</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.1797</v>
+        <v>4.5402</v>
       </c>
       <c r="C9" t="n">
-        <v>2.4203</v>
+        <v>2.629</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2671</v>
+        <v>1.3649</v>
       </c>
       <c r="E9" t="n">
-        <v>4.1797</v>
+        <v>4.5402</v>
       </c>
       <c r="F9" t="n">
-        <v>4.1797</v>
+        <v>2.4394</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2.1008</v>
       </c>
       <c r="H9" t="n">
-        <v>4.2508</v>
+        <v>2.4394</v>
       </c>
       <c r="I9" t="n">
-        <v>4.2508</v>
+        <v>2.4394</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>2.1008</v>
       </c>
       <c r="K9" t="n">
-        <v>216</v>
+        <v>145</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M9" t="n">
-        <v>4.2508</v>
+        <v>4.5402</v>
       </c>
       <c r="N9" t="n">
-        <v>216</v>
+        <v>240</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>biguzera</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.918</v>
+        <v>4.1797</v>
       </c>
       <c r="C10" t="n">
-        <v>2.2688</v>
+        <v>2.4203</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1614</v>
+        <v>1.2213</v>
       </c>
       <c r="E10" t="n">
-        <v>3.918</v>
+        <v>4.1797</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1628</v>
+        <v>4.1797</v>
       </c>
       <c r="G10" t="n">
-        <v>1.7552</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.1628</v>
+        <v>4.2508</v>
       </c>
       <c r="I10" t="n">
-        <v>2.1728</v>
+        <v>4.2508</v>
       </c>
       <c r="J10" t="n">
-        <v>1.7552</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>158</v>
+        <v>216</v>
       </c>
       <c r="L10" t="n">
-        <v>197</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.928</v>
+        <v>4.2508</v>
       </c>
       <c r="N10" t="n">
-        <v>355</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.5662</v>
+        <v>3.8151</v>
       </c>
       <c r="C11" t="n">
-        <v>2.065</v>
+        <v>2.2092</v>
       </c>
       <c r="D11" t="n">
-        <v>1.0193</v>
+        <v>1.076</v>
       </c>
       <c r="E11" t="n">
-        <v>3.5662</v>
+        <v>3.8151</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9872</v>
+        <v>3.3963</v>
       </c>
       <c r="G11" t="n">
-        <v>2.579</v>
+        <v>0.4188</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9872</v>
+        <v>3.3963</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9872</v>
+        <v>3.3963</v>
       </c>
       <c r="J11" t="n">
-        <v>2.579</v>
+        <v>0.4188</v>
       </c>
       <c r="K11" t="n">
         <v>145</v>
@@ -943,7 +943,7 @@
         <v>95</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5662</v>
+        <v>3.8151</v>
       </c>
       <c r="N11" t="n">
         <v>240</v>
@@ -952,354 +952,354 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.085</v>
+        <v>3.7007</v>
       </c>
       <c r="C12" t="n">
-        <v>1.7864</v>
+        <v>2.1429</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8249</v>
+        <v>1.0304</v>
       </c>
       <c r="E12" t="n">
-        <v>3.085</v>
+        <v>3.7007</v>
       </c>
       <c r="F12" t="n">
-        <v>3.3209</v>
+        <v>3.2476</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2359</v>
+        <v>0.4531</v>
       </c>
       <c r="H12" t="n">
-        <v>3.3209</v>
+        <v>3.2476</v>
       </c>
       <c r="I12" t="n">
-        <v>3.3209</v>
+        <v>3.2476</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.2359</v>
+        <v>0.4531</v>
       </c>
       <c r="K12" t="n">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="L12" t="n">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="M12" t="n">
-        <v>3.085</v>
+        <v>3.7007</v>
       </c>
       <c r="N12" t="n">
-        <v>191</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.0362</v>
+        <v>3.6035</v>
       </c>
       <c r="C13" t="n">
-        <v>1.7581</v>
+        <v>2.0866</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8052</v>
+        <v>0.9917</v>
       </c>
       <c r="E13" t="n">
-        <v>3.0362</v>
+        <v>3.6035</v>
       </c>
       <c r="F13" t="n">
-        <v>2.5831</v>
+        <v>3.8394</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4531</v>
+        <v>-0.2359</v>
       </c>
       <c r="H13" t="n">
-        <v>2.5831</v>
+        <v>3.8394</v>
       </c>
       <c r="I13" t="n">
-        <v>2.5831</v>
+        <v>3.8394</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4531</v>
+        <v>-0.2359</v>
       </c>
       <c r="K13" t="n">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="L13" t="n">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="M13" t="n">
-        <v>3.0362</v>
+        <v>3.6035</v>
       </c>
       <c r="N13" t="n">
-        <v>118</v>
+        <v>191</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.8308</v>
+        <v>3.5662</v>
       </c>
       <c r="C14" t="n">
-        <v>1.6392</v>
+        <v>2.065</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7222</v>
+        <v>0.9769</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8308</v>
+        <v>3.5662</v>
       </c>
       <c r="F14" t="n">
-        <v>3.4302</v>
+        <v>0.9872</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.5994</v>
+        <v>2.579</v>
       </c>
       <c r="H14" t="n">
-        <v>3.4302</v>
+        <v>0.9872</v>
       </c>
       <c r="I14" t="n">
-        <v>3.4302</v>
+        <v>0.9872</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.5994</v>
+        <v>2.579</v>
       </c>
       <c r="K14" t="n">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="L14" t="n">
-        <v>51</v>
+        <v>95</v>
       </c>
       <c r="M14" t="n">
-        <v>2.8308</v>
+        <v>3.5662</v>
       </c>
       <c r="N14" t="n">
-        <v>170</v>
+        <v>240</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.8256</v>
+        <v>3.5566</v>
       </c>
       <c r="C15" t="n">
-        <v>1.6362</v>
+        <v>2.0595</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7201</v>
+        <v>0.973</v>
       </c>
       <c r="E15" t="n">
-        <v>2.8256</v>
+        <v>3.5566</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9851</v>
+        <v>4.156</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8405</v>
+        <v>-0.5994</v>
       </c>
       <c r="H15" t="n">
-        <v>1.9851</v>
+        <v>4.2135</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9851</v>
+        <v>4.2135</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8405</v>
+        <v>-0.5994</v>
       </c>
       <c r="K15" t="n">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="L15" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="M15" t="n">
-        <v>2.8256</v>
+        <v>3.6141</v>
       </c>
       <c r="N15" t="n">
-        <v>118</v>
+        <v>170</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>Ax1Le</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.7305</v>
+        <v>3.3756</v>
       </c>
       <c r="C16" t="n">
-        <v>1.5811</v>
+        <v>1.9547</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6817</v>
+        <v>0.9009</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7305</v>
+        <v>3.3756</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3117</v>
+        <v>3.5571</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4188</v>
+        <v>-0.1815</v>
       </c>
       <c r="H16" t="n">
-        <v>2.3117</v>
+        <v>3.5571</v>
       </c>
       <c r="I16" t="n">
-        <v>2.3117</v>
+        <v>3.5571</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4188</v>
+        <v>-0.1815</v>
       </c>
       <c r="K16" t="n">
-        <v>145</v>
+        <v>122</v>
       </c>
       <c r="L16" t="n">
-        <v>95</v>
+        <v>36</v>
       </c>
       <c r="M16" t="n">
-        <v>2.7305</v>
+        <v>3.3756</v>
       </c>
       <c r="N16" t="n">
-        <v>240</v>
+        <v>158</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ax1Le</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.6544</v>
+        <v>2.9919</v>
       </c>
       <c r="C17" t="n">
-        <v>1.5371</v>
+        <v>1.7325</v>
       </c>
       <c r="D17" t="n">
-        <v>0.651</v>
+        <v>0.7481</v>
       </c>
       <c r="E17" t="n">
-        <v>2.6544</v>
+        <v>2.9919</v>
       </c>
       <c r="F17" t="n">
-        <v>2.8359</v>
+        <v>1.0249</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1815</v>
+        <v>1.967</v>
       </c>
       <c r="H17" t="n">
-        <v>2.8359</v>
+        <v>1.0249</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8359</v>
+        <v>1.0335</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1815</v>
+        <v>1.967</v>
       </c>
       <c r="K17" t="n">
-        <v>122</v>
+        <v>200</v>
       </c>
       <c r="L17" t="n">
-        <v>36</v>
+        <v>114</v>
       </c>
       <c r="M17" t="n">
-        <v>2.6544</v>
+        <v>3.0005</v>
       </c>
       <c r="N17" t="n">
-        <v>158</v>
+        <v>314</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>nexa</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.6335</v>
+        <v>2.8256</v>
       </c>
       <c r="C18" t="n">
-        <v>1.525</v>
+        <v>1.6362</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6425</v>
+        <v>0.6818</v>
       </c>
       <c r="E18" t="n">
-        <v>2.6335</v>
+        <v>2.8256</v>
       </c>
       <c r="F18" t="n">
-        <v>2.994</v>
+        <v>1.9851</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3605</v>
+        <v>0.8405</v>
       </c>
       <c r="H18" t="n">
-        <v>2.994</v>
+        <v>1.9851</v>
       </c>
       <c r="I18" t="n">
-        <v>3.0079</v>
+        <v>1.9851</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3605</v>
+        <v>0.8405</v>
       </c>
       <c r="K18" t="n">
-        <v>200</v>
+        <v>77</v>
       </c>
       <c r="L18" t="n">
-        <v>114</v>
+        <v>41</v>
       </c>
       <c r="M18" t="n">
-        <v>2.6474</v>
+        <v>2.8256</v>
       </c>
       <c r="N18" t="n">
-        <v>314</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>n0rb3r7</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.2901</v>
+        <v>2.7616</v>
       </c>
       <c r="C19" t="n">
-        <v>1.3261</v>
+        <v>1.5991</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5038</v>
+        <v>0.6563</v>
       </c>
       <c r="E19" t="n">
-        <v>2.2901</v>
+        <v>2.7616</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2901</v>
+        <v>2.7616</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2.2901</v>
+        <v>2.7616</v>
       </c>
       <c r="I19" t="n">
-        <v>2.2901</v>
+        <v>2.7616</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.2901</v>
+        <v>2.7616</v>
       </c>
       <c r="N19" t="n">
         <v>191</v>
@@ -1320,81 +1320,81 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Jimpphat</t>
+          <t>Wicadia</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.2083</v>
+        <v>2.6335</v>
       </c>
       <c r="C20" t="n">
-        <v>1.2787</v>
+        <v>1.525</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4707</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>2.2083</v>
+        <v>2.6335</v>
       </c>
       <c r="F20" t="n">
-        <v>2.6815</v>
+        <v>2.3936</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4732</v>
+        <v>0.2399</v>
       </c>
       <c r="H20" t="n">
-        <v>2.6815</v>
+        <v>2.3936</v>
       </c>
       <c r="I20" t="n">
-        <v>2.6815</v>
+        <v>2.3936</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4732</v>
+        <v>0.2399</v>
       </c>
       <c r="K20" t="n">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="L20" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="M20" t="n">
-        <v>2.2083</v>
+        <v>2.6335</v>
       </c>
       <c r="N20" t="n">
-        <v>118</v>
+        <v>170</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>nexa</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.1155</v>
+        <v>2.6223</v>
       </c>
       <c r="C21" t="n">
-        <v>1.225</v>
+        <v>1.5185</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4333</v>
+        <v>0.6008</v>
       </c>
       <c r="E21" t="n">
-        <v>2.1155</v>
+        <v>2.6223</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1485</v>
+        <v>2.9828</v>
       </c>
       <c r="G21" t="n">
-        <v>1.967</v>
+        <v>-0.3605</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1485</v>
+        <v>2.9828</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1492</v>
+        <v>3.0079</v>
       </c>
       <c r="J21" t="n">
-        <v>1.967</v>
+        <v>-0.3605</v>
       </c>
       <c r="K21" t="n">
         <v>200</v>
@@ -1403,7 +1403,7 @@
         <v>114</v>
       </c>
       <c r="M21" t="n">
-        <v>2.1162</v>
+        <v>2.6474</v>
       </c>
       <c r="N21" t="n">
         <v>314</v>
@@ -1412,415 +1412,415 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MAJ3R</t>
+          <t>n0rb3r7</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.0885</v>
+        <v>2.4311</v>
       </c>
       <c r="C22" t="n">
-        <v>1.2094</v>
+        <v>1.4078</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4223</v>
+        <v>0.5246</v>
       </c>
       <c r="E22" t="n">
-        <v>2.0885</v>
+        <v>2.4311</v>
       </c>
       <c r="F22" t="n">
-        <v>2.4291</v>
+        <v>2.4311</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3406</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2.4291</v>
+        <v>2.4311</v>
       </c>
       <c r="I22" t="n">
-        <v>2.4291</v>
+        <v>2.4311</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3406</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>119</v>
+        <v>191</v>
       </c>
       <c r="L22" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.0885</v>
+        <v>2.4311</v>
       </c>
       <c r="N22" t="n">
-        <v>170</v>
+        <v>191</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>n1ssim</t>
+          <t>Jimpphat</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.8873</v>
+        <v>2.2083</v>
       </c>
       <c r="C23" t="n">
-        <v>1.0929</v>
+        <v>1.2787</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3411</v>
+        <v>0.4359</v>
       </c>
       <c r="E23" t="n">
-        <v>1.8873</v>
+        <v>2.2083</v>
       </c>
       <c r="F23" t="n">
-        <v>1.8873</v>
+        <v>2.6815</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-0.4732</v>
       </c>
       <c r="H23" t="n">
-        <v>1.8873</v>
+        <v>2.6815</v>
       </c>
       <c r="I23" t="n">
-        <v>1.8873</v>
+        <v>2.6815</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-0.4732</v>
       </c>
       <c r="K23" t="n">
-        <v>216</v>
+        <v>77</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="M23" t="n">
-        <v>1.8873</v>
+        <v>2.2083</v>
       </c>
       <c r="N23" t="n">
-        <v>216</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.8506</v>
+        <v>2.1893</v>
       </c>
       <c r="C24" t="n">
-        <v>1.0716</v>
+        <v>1.2677</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3262</v>
+        <v>0.4283</v>
       </c>
       <c r="E24" t="n">
-        <v>1.8506</v>
+        <v>2.1893</v>
       </c>
       <c r="F24" t="n">
-        <v>2.2442</v>
+        <v>2.7833</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.3936</v>
+        <v>-0.594</v>
       </c>
       <c r="H24" t="n">
-        <v>2.2442</v>
+        <v>2.7833</v>
       </c>
       <c r="I24" t="n">
-        <v>2.2547</v>
+        <v>2.7833</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.3936</v>
+        <v>-0.594</v>
       </c>
       <c r="K24" t="n">
-        <v>158</v>
+        <v>106</v>
       </c>
       <c r="L24" t="n">
-        <v>197</v>
+        <v>85</v>
       </c>
       <c r="M24" t="n">
-        <v>1.8611</v>
+        <v>2.1893</v>
       </c>
       <c r="N24" t="n">
-        <v>355</v>
+        <v>191</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Queenix</t>
+          <t>MAJ3R</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.8498</v>
+        <v>2.1799</v>
       </c>
       <c r="C25" t="n">
-        <v>1.0711</v>
+        <v>1.2623</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3259</v>
+        <v>0.4246</v>
       </c>
       <c r="E25" t="n">
-        <v>1.8498</v>
+        <v>2.1799</v>
       </c>
       <c r="F25" t="n">
-        <v>1.8498</v>
+        <v>2.5205</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-0.3406</v>
       </c>
       <c r="H25" t="n">
-        <v>1.8498</v>
+        <v>2.5205</v>
       </c>
       <c r="I25" t="n">
-        <v>1.8498</v>
+        <v>2.5205</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-0.3406</v>
       </c>
       <c r="K25" t="n">
-        <v>175</v>
+        <v>119</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M25" t="n">
-        <v>1.8498</v>
+        <v>2.1799</v>
       </c>
       <c r="N25" t="n">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.7974</v>
+        <v>2.1118</v>
       </c>
       <c r="C26" t="n">
-        <v>1.0408</v>
+        <v>1.2229</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3047</v>
+        <v>0.3974</v>
       </c>
       <c r="E26" t="n">
-        <v>1.7974</v>
+        <v>2.1118</v>
       </c>
       <c r="F26" t="n">
-        <v>2.3914</v>
+        <v>1.7884</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.594</v>
+        <v>0.3234</v>
       </c>
       <c r="H26" t="n">
-        <v>2.3914</v>
+        <v>1.7884</v>
       </c>
       <c r="I26" t="n">
-        <v>2.3914</v>
+        <v>1.7884</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.594</v>
+        <v>0.3234</v>
       </c>
       <c r="K26" t="n">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="L26" t="n">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="M26" t="n">
-        <v>1.7974</v>
+        <v>2.1118</v>
       </c>
       <c r="N26" t="n">
-        <v>191</v>
+        <v>158</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Wicadia</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.7923</v>
+        <v>2.0579</v>
       </c>
       <c r="C27" t="n">
-        <v>1.0378</v>
+        <v>1.1916</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3027</v>
+        <v>0.376</v>
       </c>
       <c r="E27" t="n">
-        <v>1.7923</v>
+        <v>2.0579</v>
       </c>
       <c r="F27" t="n">
-        <v>1.5524</v>
+        <v>2.4515</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2399</v>
+        <v>-0.3936</v>
       </c>
       <c r="H27" t="n">
-        <v>1.5524</v>
+        <v>2.4515</v>
       </c>
       <c r="I27" t="n">
-        <v>1.5524</v>
+        <v>2.4721</v>
       </c>
       <c r="J27" t="n">
-        <v>0.2399</v>
+        <v>-0.3936</v>
       </c>
       <c r="K27" t="n">
-        <v>119</v>
+        <v>158</v>
       </c>
       <c r="L27" t="n">
-        <v>51</v>
+        <v>197</v>
       </c>
       <c r="M27" t="n">
-        <v>1.7923</v>
+        <v>2.0785</v>
       </c>
       <c r="N27" t="n">
-        <v>170</v>
+        <v>355</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.4891</v>
+        <v>1.9599</v>
       </c>
       <c r="C28" t="n">
-        <v>0.8623</v>
+        <v>1.1349</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1802</v>
+        <v>0.3369</v>
       </c>
       <c r="E28" t="n">
-        <v>1.4891</v>
+        <v>1.9599</v>
       </c>
       <c r="F28" t="n">
-        <v>1.4891</v>
+        <v>0.4041</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1.5558</v>
       </c>
       <c r="H28" t="n">
-        <v>1.4891</v>
+        <v>0.4041</v>
       </c>
       <c r="I28" t="n">
-        <v>1.4891</v>
+        <v>0.4075</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1.5558</v>
       </c>
       <c r="K28" t="n">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="M28" t="n">
-        <v>1.4891</v>
+        <v>1.9633</v>
       </c>
       <c r="N28" t="n">
-        <v>191</v>
+        <v>314</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>n1ssim</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.3185</v>
+        <v>1.8873</v>
       </c>
       <c r="C29" t="n">
-        <v>0.7635</v>
+        <v>1.0929</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1113</v>
+        <v>0.308</v>
       </c>
       <c r="E29" t="n">
-        <v>1.3185</v>
+        <v>1.8873</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.2372</v>
+        <v>1.8873</v>
       </c>
       <c r="G29" t="n">
-        <v>1.5558</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.2372</v>
+        <v>1.8873</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2383</v>
+        <v>1.8873</v>
       </c>
       <c r="J29" t="n">
-        <v>1.5558</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="L29" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.3175</v>
+        <v>1.8873</v>
       </c>
       <c r="N29" t="n">
-        <v>314</v>
+        <v>216</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>Queenix</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.181</v>
+        <v>1.8498</v>
       </c>
       <c r="C30" t="n">
-        <v>0.6839</v>
+        <v>1.0711</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0557</v>
+        <v>0.2931</v>
       </c>
       <c r="E30" t="n">
-        <v>1.181</v>
+        <v>1.8498</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8576</v>
+        <v>1.8498</v>
       </c>
       <c r="G30" t="n">
-        <v>0.3234</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.8576</v>
+        <v>1.8498</v>
       </c>
       <c r="I30" t="n">
-        <v>0.8576</v>
+        <v>1.8498</v>
       </c>
       <c r="J30" t="n">
-        <v>0.3234</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>122</v>
+        <v>175</v>
       </c>
       <c r="L30" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.181</v>
+        <v>1.8498</v>
       </c>
       <c r="N30" t="n">
-        <v>158</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31">
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.1304</v>
+        <v>1.4492</v>
       </c>
       <c r="C31" t="n">
-        <v>0.6546</v>
+        <v>0.8391999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0353</v>
+        <v>0.1335</v>
       </c>
       <c r="E31" t="n">
-        <v>1.1304</v>
+        <v>1.4492</v>
       </c>
       <c r="F31" t="n">
-        <v>2.1304</v>
+        <v>2.4492</v>
       </c>
       <c r="G31" t="n">
         <v>-1</v>
       </c>
       <c r="H31" t="n">
-        <v>2.1304</v>
+        <v>2.4492</v>
       </c>
       <c r="I31" t="n">
-        <v>2.1304</v>
+        <v>2.4492</v>
       </c>
       <c r="J31" t="n">
         <v>-1</v>
@@ -1863,7 +1863,7 @@
         <v>41</v>
       </c>
       <c r="M31" t="n">
-        <v>1.1304</v>
+        <v>1.4492</v>
       </c>
       <c r="N31" t="n">
         <v>118</v>
@@ -1872,78 +1872,78 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.1104</v>
+        <v>1.3347</v>
       </c>
       <c r="C32" t="n">
-        <v>0.643</v>
+        <v>0.7729</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0272</v>
+        <v>0.0878</v>
       </c>
       <c r="E32" t="n">
-        <v>1.1104</v>
+        <v>1.3347</v>
       </c>
       <c r="F32" t="n">
-        <v>0.4951</v>
+        <v>1.3347</v>
       </c>
       <c r="G32" t="n">
-        <v>0.6153</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.4951</v>
+        <v>1.3347</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4974</v>
+        <v>1.3347</v>
       </c>
       <c r="J32" t="n">
-        <v>0.6153</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>158</v>
+        <v>119</v>
       </c>
       <c r="L32" t="n">
-        <v>197</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.1127</v>
+        <v>1.3347</v>
       </c>
       <c r="N32" t="n">
-        <v>355</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>hallzerk</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.1085</v>
+        <v>1.3063</v>
       </c>
       <c r="C33" t="n">
-        <v>0.6419</v>
+        <v>0.7564</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0264</v>
+        <v>0.0765</v>
       </c>
       <c r="E33" t="n">
-        <v>1.1085</v>
+        <v>1.3063</v>
       </c>
       <c r="F33" t="n">
-        <v>1.1085</v>
+        <v>1.3063</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.1085</v>
+        <v>1.3063</v>
       </c>
       <c r="I33" t="n">
-        <v>1.1085</v>
+        <v>1.3063</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.1085</v>
+        <v>1.3063</v>
       </c>
       <c r="N33" t="n">
         <v>203</v>
@@ -1964,311 +1964,311 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.0396</v>
+        <v>1.1171</v>
       </c>
       <c r="C34" t="n">
-        <v>0.602</v>
+        <v>0.6469</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.0014</v>
+        <v>0.0011</v>
       </c>
       <c r="E34" t="n">
-        <v>1.0396</v>
+        <v>1.1171</v>
       </c>
       <c r="F34" t="n">
-        <v>1.0396</v>
+        <v>2.1171</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H34" t="n">
-        <v>1.0396</v>
+        <v>2.1171</v>
       </c>
       <c r="I34" t="n">
-        <v>1.0396</v>
+        <v>2.1171</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K34" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M34" t="n">
-        <v>1.0396</v>
+        <v>1.1171</v>
       </c>
       <c r="N34" t="n">
-        <v>119</v>
+        <v>158</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>hallzerk</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.9396</v>
+        <v>1.1085</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5441</v>
+        <v>0.6419</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0418</v>
+        <v>-0.0023</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9396</v>
+        <v>1.1085</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9396</v>
+        <v>1.1085</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.9396</v>
+        <v>1.1085</v>
       </c>
       <c r="I35" t="n">
-        <v>0.9396</v>
+        <v>1.1085</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>131</v>
+        <v>203</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.9396</v>
+        <v>1.1085</v>
       </c>
       <c r="N35" t="n">
-        <v>131</v>
+        <v>203</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Boombl4</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8424</v>
+        <v>1.1085</v>
       </c>
       <c r="C36" t="n">
-        <v>0.4878</v>
+        <v>0.6419</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.08110000000000001</v>
+        <v>-0.0023</v>
       </c>
       <c r="E36" t="n">
-        <v>0.8424</v>
+        <v>1.1085</v>
       </c>
       <c r="F36" t="n">
-        <v>1.6668</v>
+        <v>0.4932</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.8244</v>
+        <v>0.6153</v>
       </c>
       <c r="H36" t="n">
-        <v>1.6668</v>
+        <v>0.4932</v>
       </c>
       <c r="I36" t="n">
-        <v>1.6668</v>
+        <v>0.4974</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.8244</v>
+        <v>0.6153</v>
       </c>
       <c r="K36" t="n">
-        <v>122</v>
+        <v>158</v>
       </c>
       <c r="L36" t="n">
-        <v>36</v>
+        <v>197</v>
       </c>
       <c r="M36" t="n">
-        <v>0.8424</v>
+        <v>1.1127</v>
       </c>
       <c r="N36" t="n">
-        <v>158</v>
+        <v>355</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8167</v>
+        <v>1.0149</v>
       </c>
       <c r="C37" t="n">
-        <v>0.4729</v>
+        <v>0.5877</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.0914</v>
+        <v>-0.0396</v>
       </c>
       <c r="E37" t="n">
-        <v>0.8167</v>
+        <v>1.0149</v>
       </c>
       <c r="F37" t="n">
-        <v>1.0105</v>
+        <v>1.0149</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.1938</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1.0105</v>
+        <v>1.0149</v>
       </c>
       <c r="I37" t="n">
-        <v>1.0105</v>
+        <v>1.0149</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.1938</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="L37" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.8167</v>
+        <v>1.0149</v>
       </c>
       <c r="N37" t="n">
-        <v>191</v>
+        <v>131</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7231</v>
+        <v>0.9193</v>
       </c>
       <c r="C38" t="n">
-        <v>0.4187</v>
+        <v>0.5323</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1292</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="E38" t="n">
-        <v>0.7231</v>
+        <v>0.9193</v>
       </c>
       <c r="F38" t="n">
-        <v>0.7231</v>
+        <v>1.5298</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>-0.6105</v>
       </c>
       <c r="H38" t="n">
-        <v>0.7231</v>
+        <v>1.5298</v>
       </c>
       <c r="I38" t="n">
-        <v>0.7231</v>
+        <v>1.5298</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>-0.6105</v>
       </c>
       <c r="K38" t="n">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M38" t="n">
-        <v>0.7231</v>
+        <v>0.9193</v>
       </c>
       <c r="N38" t="n">
-        <v>106</v>
+        <v>158</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Patti</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7121</v>
+        <v>0.8489</v>
       </c>
       <c r="C39" t="n">
-        <v>0.4123</v>
+        <v>0.4916</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1337</v>
+        <v>-0.1057</v>
       </c>
       <c r="E39" t="n">
-        <v>0.7121</v>
+        <v>0.8489</v>
       </c>
       <c r="F39" t="n">
-        <v>0.7121</v>
+        <v>1.0427</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>-0.1938</v>
       </c>
       <c r="H39" t="n">
-        <v>0.7121</v>
+        <v>1.0427</v>
       </c>
       <c r="I39" t="n">
-        <v>0.7121</v>
+        <v>1.0427</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>-0.1938</v>
       </c>
       <c r="K39" t="n">
-        <v>175</v>
+        <v>106</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M39" t="n">
-        <v>0.7121</v>
+        <v>0.8489</v>
       </c>
       <c r="N39" t="n">
-        <v>175</v>
+        <v>191</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>Boombl4</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6515</v>
+        <v>0.8424</v>
       </c>
       <c r="C40" t="n">
-        <v>0.3773</v>
+        <v>0.4878</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.1582</v>
+        <v>-0.1083</v>
       </c>
       <c r="E40" t="n">
-        <v>0.6515</v>
+        <v>0.8424</v>
       </c>
       <c r="F40" t="n">
-        <v>1.262</v>
+        <v>1.6668</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.6105</v>
+        <v>-0.8244</v>
       </c>
       <c r="H40" t="n">
-        <v>1.262</v>
+        <v>1.6668</v>
       </c>
       <c r="I40" t="n">
-        <v>1.262</v>
+        <v>1.6668</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.6105</v>
+        <v>-0.8244</v>
       </c>
       <c r="K40" t="n">
         <v>122</v>
@@ -2277,7 +2277,7 @@
         <v>36</v>
       </c>
       <c r="M40" t="n">
-        <v>0.6515</v>
+        <v>0.8424</v>
       </c>
       <c r="N40" t="n">
         <v>158</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6385</v>
+        <v>0.8177</v>
       </c>
       <c r="C41" t="n">
-        <v>0.3697</v>
+        <v>0.4735</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.1634</v>
+        <v>-0.1181</v>
       </c>
       <c r="E41" t="n">
-        <v>0.6385</v>
+        <v>0.8177</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.3728</v>
+        <v>-0.1936</v>
       </c>
       <c r="G41" t="n">
         <v>1.0113</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.3728</v>
+        <v>-0.1936</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3728</v>
+        <v>-0.1936</v>
       </c>
       <c r="J41" t="n">
         <v>1.0113</v>
@@ -2323,7 +2323,7 @@
         <v>95</v>
       </c>
       <c r="M41" t="n">
-        <v>0.6385000000000001</v>
+        <v>0.8177000000000001</v>
       </c>
       <c r="N41" t="n">
         <v>240</v>
@@ -2332,124 +2332,124 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>lux</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4128</v>
+        <v>0.7231</v>
       </c>
       <c r="C42" t="n">
-        <v>0.239</v>
+        <v>0.4187</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2546</v>
+        <v>-0.1558</v>
       </c>
       <c r="E42" t="n">
-        <v>0.4128</v>
+        <v>0.7231</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4128</v>
+        <v>0.7231</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.4128</v>
+        <v>0.7231</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4128</v>
+        <v>0.7231</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>216</v>
+        <v>106</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.4128</v>
+        <v>0.7231</v>
       </c>
       <c r="N42" t="n">
-        <v>216</v>
+        <v>106</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>Patti</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.3198</v>
+        <v>0.7121</v>
       </c>
       <c r="C43" t="n">
-        <v>0.1852</v>
+        <v>0.4123</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2922</v>
+        <v>-0.1602</v>
       </c>
       <c r="E43" t="n">
-        <v>0.3198</v>
+        <v>0.7121</v>
       </c>
       <c r="F43" t="n">
-        <v>0.3198</v>
+        <v>0.7121</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.3198</v>
+        <v>0.7121</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3198</v>
+        <v>0.7121</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>119</v>
+        <v>175</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.3198</v>
+        <v>0.7121</v>
       </c>
       <c r="N43" t="n">
-        <v>119</v>
+        <v>175</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>decenty</t>
+          <t>noway</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.2596</v>
+        <v>0.4531</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1503</v>
+        <v>0.2624</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.3165</v>
+        <v>-0.2634</v>
       </c>
       <c r="E44" t="n">
-        <v>0.2596</v>
+        <v>0.4531</v>
       </c>
       <c r="F44" t="n">
-        <v>0.2596</v>
+        <v>0.4531</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.2596</v>
+        <v>0.4531</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2596</v>
+        <v>0.4531</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.2596</v>
+        <v>0.4531</v>
       </c>
       <c r="N44" t="n">
         <v>119</v>
@@ -2470,967 +2470,967 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.256</v>
+        <v>0.4272</v>
       </c>
       <c r="C45" t="n">
-        <v>0.1482</v>
+        <v>0.2474</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3179</v>
+        <v>-0.2737</v>
       </c>
       <c r="E45" t="n">
-        <v>0.256</v>
+        <v>0.4272</v>
       </c>
       <c r="F45" t="n">
-        <v>0.256</v>
+        <v>0.4272</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.256</v>
+        <v>0.4272</v>
       </c>
       <c r="I45" t="n">
-        <v>0.256</v>
+        <v>0.4272</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>203</v>
+        <v>119</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.256</v>
+        <v>0.4272</v>
       </c>
       <c r="N45" t="n">
-        <v>203</v>
+        <v>119</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Nodios</t>
+          <t>lux</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.2316</v>
+        <v>0.4128</v>
       </c>
       <c r="C46" t="n">
-        <v>0.1341</v>
+        <v>0.239</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3278</v>
+        <v>-0.2795</v>
       </c>
       <c r="E46" t="n">
-        <v>0.2316</v>
+        <v>0.4128</v>
       </c>
       <c r="F46" t="n">
-        <v>0.2316</v>
+        <v>0.4128</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.2316</v>
+        <v>0.4128</v>
       </c>
       <c r="I46" t="n">
-        <v>0.2316</v>
+        <v>0.4128</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>175</v>
+        <v>216</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.2316</v>
+        <v>0.4128</v>
       </c>
       <c r="N46" t="n">
-        <v>175</v>
+        <v>216</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>VINI</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.1962</v>
+        <v>0.3729</v>
       </c>
       <c r="C47" t="n">
-        <v>0.1136</v>
+        <v>0.2159</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3421</v>
+        <v>-0.2953</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1962</v>
+        <v>0.3729</v>
       </c>
       <c r="F47" t="n">
-        <v>0.1962</v>
+        <v>0.3729</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.1962</v>
+        <v>0.3729</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1962</v>
+        <v>0.3729</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>119</v>
+        <v>203</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.1962</v>
+        <v>0.3729</v>
       </c>
       <c r="N47" t="n">
-        <v>119</v>
+        <v>203</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>mir</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.1864</v>
+        <v>0.3523</v>
       </c>
       <c r="C48" t="n">
-        <v>0.1079</v>
+        <v>0.204</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3461</v>
+        <v>-0.3036</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1864</v>
+        <v>0.3523</v>
       </c>
       <c r="F48" t="n">
-        <v>1.1864</v>
+        <v>0.3523</v>
       </c>
       <c r="G48" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>1.1864</v>
+        <v>0.3523</v>
       </c>
       <c r="I48" t="n">
-        <v>1.1864</v>
+        <v>0.3523</v>
       </c>
       <c r="J48" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>122</v>
+        <v>191</v>
       </c>
       <c r="L48" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.1863999999999999</v>
+        <v>0.3523</v>
       </c>
       <c r="N48" t="n">
-        <v>158</v>
+        <v>191</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>mir</t>
+          <t>decenty</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.0863</v>
+        <v>0.2596</v>
       </c>
       <c r="C49" t="n">
-        <v>0.05</v>
+        <v>0.1503</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3865</v>
+        <v>-0.3405</v>
       </c>
       <c r="E49" t="n">
-        <v>0.0863</v>
+        <v>0.2596</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0863</v>
+        <v>0.2596</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0863</v>
+        <v>0.2596</v>
       </c>
       <c r="I49" t="n">
-        <v>0.0863</v>
+        <v>0.2596</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>191</v>
+        <v>119</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.0863</v>
+        <v>0.2596</v>
       </c>
       <c r="N49" t="n">
-        <v>191</v>
+        <v>119</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>nicoodoz</t>
+          <t>Nodios</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.0294</v>
+        <v>0.2316</v>
       </c>
       <c r="C50" t="n">
-        <v>0.017</v>
+        <v>0.1341</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4095</v>
+        <v>-0.3516</v>
       </c>
       <c r="E50" t="n">
-        <v>0.0294</v>
+        <v>0.2316</v>
       </c>
       <c r="F50" t="n">
-        <v>0.0294</v>
+        <v>0.2316</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.0294</v>
+        <v>0.2316</v>
       </c>
       <c r="I50" t="n">
-        <v>0.0294</v>
+        <v>0.2316</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>119</v>
+        <v>175</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.0294</v>
+        <v>0.2316</v>
       </c>
       <c r="N50" t="n">
-        <v>119</v>
+        <v>175</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>VINI</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.0146</v>
+        <v>0.1962</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.1136</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4273</v>
+        <v>-0.3657</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.0146</v>
+        <v>0.1962</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.0146</v>
+        <v>0.1962</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.0146</v>
+        <v>0.1962</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.0146</v>
+        <v>0.1962</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.0146</v>
+        <v>0.1962</v>
       </c>
       <c r="N51" t="n">
-        <v>131</v>
+        <v>119</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.0989</v>
+        <v>0.1552</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.0573</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4613</v>
+        <v>-0.3821</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.0989</v>
+        <v>0.1552</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.0989</v>
+        <v>0.1552</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.0989</v>
+        <v>0.1552</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.0989</v>
+        <v>0.1552</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>131</v>
+        <v>191</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.0989</v>
+        <v>0.1552</v>
       </c>
       <c r="N52" t="n">
-        <v>131</v>
+        <v>191</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>nicoodoz</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.1346</v>
+        <v>0.0294</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.0779</v>
+        <v>0.017</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4757</v>
+        <v>-0.4322</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.1346</v>
+        <v>0.0294</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.1346</v>
+        <v>0.0294</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.1346</v>
+        <v>0.0294</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1346</v>
+        <v>0.0294</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>203</v>
+        <v>119</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.1346</v>
+        <v>0.0294</v>
       </c>
       <c r="N53" t="n">
-        <v>203</v>
+        <v>119</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.137</v>
+        <v>-0.0146</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.0793</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4767</v>
+        <v>-0.4497</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.137</v>
+        <v>-0.0146</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.137</v>
+        <v>-0.0146</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.137</v>
+        <v>-0.0146</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.137</v>
+        <v>-0.0146</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.137</v>
+        <v>-0.0146</v>
       </c>
       <c r="N54" t="n">
-        <v>119</v>
+        <v>131</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.1385</v>
+        <v>-0.0989</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.08019999999999999</v>
+        <v>-0.0573</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.4773</v>
+        <v>-0.4833</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.1385</v>
+        <v>-0.0989</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.1385</v>
+        <v>-0.0989</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.1385</v>
+        <v>-0.0989</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1385</v>
+        <v>-0.0989</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>203</v>
+        <v>131</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.1385</v>
+        <v>-0.0989</v>
       </c>
       <c r="N55" t="n">
-        <v>203</v>
+        <v>131</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>kraghen</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.1857</v>
+        <v>-0.1223</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.1075</v>
+        <v>-0.0708</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.4964</v>
+        <v>-0.4926</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.1857</v>
+        <v>-0.1223</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.1857</v>
+        <v>0.3394</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>-0.4617</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.1857</v>
+        <v>0.3394</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.1857</v>
+        <v>0.3394</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>-0.4617</v>
       </c>
       <c r="K56" t="n">
-        <v>175</v>
+        <v>106</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.1857</v>
+        <v>-0.1223</v>
       </c>
       <c r="N56" t="n">
-        <v>175</v>
+        <v>191</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.3216</v>
+        <v>-0.1346</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.1862</v>
+        <v>-0.0779</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5513</v>
+        <v>-0.4975</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.3216</v>
+        <v>-0.1346</v>
       </c>
       <c r="F57" t="n">
-        <v>0.1401</v>
+        <v>-0.1346</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.4617</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0.1401</v>
+        <v>-0.1346</v>
       </c>
       <c r="I57" t="n">
-        <v>0.1401</v>
+        <v>-0.1346</v>
       </c>
       <c r="J57" t="n">
-        <v>-0.4617</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>106</v>
+        <v>203</v>
       </c>
       <c r="L57" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.3216</v>
+        <v>-0.1346</v>
       </c>
       <c r="N57" t="n">
-        <v>191</v>
+        <v>203</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.3338</v>
+        <v>-0.137</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.1933</v>
+        <v>-0.0793</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5562</v>
+        <v>-0.4985</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.3338</v>
+        <v>-0.137</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.3338</v>
+        <v>-0.137</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.3338</v>
+        <v>-0.137</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.3338</v>
+        <v>-0.137</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>191</v>
+        <v>119</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.3338</v>
+        <v>-0.137</v>
       </c>
       <c r="N58" t="n">
-        <v>191</v>
+        <v>119</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senzu</t>
+          <t>kraghen</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.3367</v>
+        <v>-0.1857</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.195</v>
+        <v>-0.1075</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5574</v>
+        <v>-0.5179</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.3367</v>
+        <v>-0.1857</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.3367</v>
+        <v>-0.1857</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.3367</v>
+        <v>-0.1857</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.3367</v>
+        <v>-0.1857</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>131</v>
+        <v>175</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.3367</v>
+        <v>-0.1857</v>
       </c>
       <c r="N59" t="n">
-        <v>131</v>
+        <v>175</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.4014</v>
+        <v>-0.1924</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.2324</v>
+        <v>-0.1114</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5835</v>
+        <v>-0.5206</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.4014</v>
+        <v>-0.1924</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.4014</v>
+        <v>-0.0189</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>-0.1735</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.4014</v>
+        <v>-0.0189</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.4014</v>
+        <v>-0.0189</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>-0.1735</v>
       </c>
       <c r="K60" t="n">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.4014</v>
+        <v>-0.1924</v>
       </c>
       <c r="N60" t="n">
-        <v>131</v>
+        <v>170</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>Senzu</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.4269</v>
+        <v>-0.3367</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.2472</v>
+        <v>-0.195</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.5938</v>
+        <v>-0.5780999999999999</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.4269</v>
+        <v>-0.3367</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.7514999999999999</v>
+        <v>-0.3367</v>
       </c>
       <c r="G61" t="n">
-        <v>0.3246</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.7514999999999999</v>
+        <v>-0.3367</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.755</v>
+        <v>-0.3367</v>
       </c>
       <c r="J61" t="n">
-        <v>0.3246</v>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>158</v>
+        <v>131</v>
       </c>
       <c r="L61" t="n">
-        <v>197</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.4304</v>
+        <v>-0.3367</v>
       </c>
       <c r="N61" t="n">
-        <v>355</v>
+        <v>131</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Calyx</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.4563</v>
+        <v>-0.4014</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.2642</v>
+        <v>-0.2324</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6057</v>
+        <v>-0.6038</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.4563</v>
+        <v>-0.4014</v>
       </c>
       <c r="F62" t="n">
-        <v>-1.2692</v>
+        <v>-0.4014</v>
       </c>
       <c r="G62" t="n">
-        <v>0.8129</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-1.2692</v>
+        <v>-0.4014</v>
       </c>
       <c r="I62" t="n">
-        <v>-1.2692</v>
+        <v>-0.4014</v>
       </c>
       <c r="J62" t="n">
-        <v>0.8129</v>
+        <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="L62" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.4563000000000001</v>
+        <v>-0.4014</v>
       </c>
       <c r="N62" t="n">
-        <v>170</v>
+        <v>131</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>noway</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.4753</v>
+        <v>-0.4241</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.2752</v>
+        <v>-0.2456</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6133999999999999</v>
+        <v>-0.6129</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.4753</v>
+        <v>-0.4241</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.4753</v>
+        <v>-0.7487</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>0.3246</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.4753</v>
+        <v>-0.7487</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.4753</v>
+        <v>-0.755</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>0.3246</v>
       </c>
       <c r="K63" t="n">
-        <v>119</v>
+        <v>158</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.4753</v>
+        <v>-0.4304</v>
       </c>
       <c r="N63" t="n">
-        <v>119</v>
+        <v>355</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>Calyx</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.5441</v>
+        <v>-0.4563</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.3151</v>
+        <v>-0.2642</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.6412</v>
+        <v>-0.6257</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.5441</v>
+        <v>-0.4563</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.5441</v>
+        <v>-1.2692</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>0.8129</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.5441</v>
+        <v>-1.2692</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.5441</v>
+        <v>-1.2692</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>0.8129</v>
       </c>
       <c r="K64" t="n">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.5441</v>
+        <v>-0.4563000000000001</v>
       </c>
       <c r="N64" t="n">
-        <v>106</v>
+        <v>170</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.835</v>
+        <v>-0.5441</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.4835</v>
+        <v>-0.3151</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7587</v>
+        <v>-0.6607</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.835</v>
+        <v>-0.5441</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.6615</v>
+        <v>-0.5441</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.1735</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.6615</v>
+        <v>-0.5441</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.6615</v>
+        <v>-0.5441</v>
       </c>
       <c r="J65" t="n">
-        <v>-0.1735</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="L65" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.835</v>
+        <v>-0.5441</v>
       </c>
       <c r="N65" t="n">
-        <v>170</v>
+        <v>106</v>
       </c>
     </row>
     <row r="66">
@@ -3446,7 +3446,7 @@
         <v>-0.6115</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.848</v>
+        <v>-0.8647</v>
       </c>
       <c r="E66" t="n">
         <v>-1.0561</v>
@@ -3492,7 +3492,7 @@
         <v>-0.6915</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.9038</v>
+        <v>-0.9196</v>
       </c>
       <c r="E67" t="n">
         <v>-1.1941</v>
@@ -3538,7 +3538,7 @@
         <v>-0.6916</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.9038</v>
+        <v>-0.9197</v>
       </c>
       <c r="E68" t="n">
         <v>-1.1943</v>
@@ -3584,7 +3584,7 @@
         <v>-0.7143</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.9197</v>
+        <v>-0.9354</v>
       </c>
       <c r="E69" t="n">
         <v>-1.2336</v>
@@ -3624,28 +3624,28 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1.3642</v>
+        <v>-1.2858</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.79</v>
+        <v>-0.7446</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9725</v>
+        <v>-0.9562</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.3642</v>
+        <v>-1.2858</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.3642</v>
+        <v>-1.2858</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-1.3642</v>
+        <v>-1.2858</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.3642</v>
+        <v>-1.2858</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -3657,7 +3657,7 @@
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-1.3642</v>
+        <v>-1.2858</v>
       </c>
       <c r="N70" t="n">
         <v>216</v>
@@ -3676,7 +3676,7 @@
         <v>-0.8018</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9808</v>
+        <v>-0.9956</v>
       </c>
       <c r="E71" t="n">
         <v>-1.3847</v>
@@ -3722,7 +3722,7 @@
         <v>-0.8809</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.0359</v>
+        <v>-1.05</v>
       </c>
       <c r="E72" t="n">
         <v>-1.5213</v>
@@ -3768,7 +3768,7 @@
         <v>-0.908</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0548</v>
+        <v>-1.0686</v>
       </c>
       <c r="E73" t="n">
         <v>-1.568</v>
@@ -3814,7 +3814,7 @@
         <v>-1.3086</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.3343</v>
+        <v>-1.3443</v>
       </c>
       <c r="E74" t="n">
         <v>-2.2599</v>
@@ -3860,7 +3860,7 @@
         <v>-1.3296</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.3489</v>
+        <v>-1.3587</v>
       </c>
       <c r="E75" t="n">
         <v>-2.2961</v>
@@ -3906,7 +3906,7 @@
         <v>-1.3393</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.3557</v>
+        <v>-1.3654</v>
       </c>
       <c r="E76" t="n">
         <v>-2.3129</v>
@@ -3952,7 +3952,7 @@
         <v>-1.4094</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.4046</v>
+        <v>-1.4136</v>
       </c>
       <c r="E77" t="n">
         <v>-2.4339</v>
@@ -3998,7 +3998,7 @@
         <v>-1.5699</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.5166</v>
+        <v>-1.524</v>
       </c>
       <c r="E78" t="n">
         <v>-2.7111</v>
@@ -4038,25 +4038,25 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-3.1997</v>
+        <v>-3.1879</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.8528</v>
+        <v>-1.846</v>
       </c>
       <c r="D79" t="n">
         <v>-1.714</v>
       </c>
       <c r="E79" t="n">
-        <v>-3.1997</v>
+        <v>-3.1879</v>
       </c>
       <c r="F79" t="n">
-        <v>-3.1591</v>
+        <v>-3.1473</v>
       </c>
       <c r="G79" t="n">
         <v>-0.0406</v>
       </c>
       <c r="H79" t="n">
-        <v>-3.1591</v>
+        <v>-3.1473</v>
       </c>
       <c r="I79" t="n">
         <v>-3.1738</v>
@@ -4084,25 +4084,25 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-5.2374</v>
+        <v>-5.2141</v>
       </c>
       <c r="C80" t="n">
-        <v>-3.0328</v>
+        <v>-3.0193</v>
       </c>
       <c r="D80" t="n">
-        <v>-2.5372</v>
+        <v>-2.5212</v>
       </c>
       <c r="E80" t="n">
-        <v>-5.2374</v>
+        <v>-5.2141</v>
       </c>
       <c r="F80" t="n">
-        <v>-3.128</v>
+        <v>-3.1047</v>
       </c>
       <c r="G80" t="n">
         <v>-2.1094</v>
       </c>
       <c r="H80" t="n">
-        <v>-3.128</v>
+        <v>-3.1047</v>
       </c>
       <c r="I80" t="n">
         <v>-3.1572</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-5.2599</v>
+        <v>-5.2329</v>
       </c>
       <c r="C81" t="n">
-        <v>-3.0458</v>
+        <v>-3.0302</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.5462</v>
+        <v>-2.5287</v>
       </c>
       <c r="E81" t="n">
-        <v>-5.2599</v>
+        <v>-5.2329</v>
       </c>
       <c r="F81" t="n">
-        <v>-3.631</v>
+        <v>-3.604</v>
       </c>
       <c r="G81" t="n">
         <v>-1.6289</v>
       </c>
       <c r="H81" t="n">
-        <v>-3.631</v>
+        <v>-3.604</v>
       </c>
       <c r="I81" t="n">
         <v>-3.6649</v>

--- a/database/event/7148/event_7148_evp_summary.xlsx
+++ b/database/event/7148/event_7148_evp_summary.xlsx
@@ -496,16 +496,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.3416</v>
+        <v>8.7883</v>
       </c>
       <c r="C2" t="n">
-        <v>4.8303</v>
+        <v>5.0889</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1731</v>
+        <v>3.3117</v>
       </c>
       <c r="E2" t="n">
-        <v>8.3416</v>
+        <v>8.7883</v>
       </c>
       <c r="F2" t="n">
         <v>3.1001</v>
@@ -542,16 +542,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.1409</v>
+        <v>8.6172</v>
       </c>
       <c r="C3" t="n">
-        <v>4.7141</v>
+        <v>4.9899</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0817</v>
+        <v>3.2353</v>
       </c>
       <c r="E3" t="n">
-        <v>8.1409</v>
+        <v>8.6172</v>
       </c>
       <c r="F3" t="n">
         <v>5.1049</v>
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.3194</v>
+        <v>6.485</v>
       </c>
       <c r="C4" t="n">
-        <v>3.6593</v>
+        <v>3.7552</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2525</v>
+        <v>2.2829</v>
       </c>
       <c r="E4" t="n">
-        <v>6.3194</v>
+        <v>6.485</v>
       </c>
       <c r="F4" t="n">
         <v>1.7542</v>
@@ -634,16 +634,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.7615</v>
+        <v>5.8033</v>
       </c>
       <c r="C5" t="n">
-        <v>3.3363</v>
+        <v>3.3605</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9985</v>
+        <v>1.9784</v>
       </c>
       <c r="E5" t="n">
-        <v>5.7615</v>
+        <v>5.8033</v>
       </c>
       <c r="F5" t="n">
         <v>2.8385</v>
@@ -680,16 +680,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.6086</v>
+        <v>5.6821</v>
       </c>
       <c r="C6" t="n">
-        <v>3.2477</v>
+        <v>3.2903</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9289</v>
+        <v>1.9242</v>
       </c>
       <c r="E6" t="n">
-        <v>5.6086</v>
+        <v>5.6821</v>
       </c>
       <c r="F6" t="n">
         <v>2.4282</v>
@@ -726,16 +726,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.9669</v>
+        <v>5.0202</v>
       </c>
       <c r="C7" t="n">
-        <v>2.8761</v>
+        <v>2.907</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6368</v>
+        <v>1.6286</v>
       </c>
       <c r="E7" t="n">
-        <v>4.9669</v>
+        <v>5.0202</v>
       </c>
       <c r="F7" t="n">
         <v>2.7551</v>
@@ -772,16 +772,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.4177</v>
+        <v>4.9403</v>
       </c>
       <c r="C8" t="n">
-        <v>2.5581</v>
+        <v>2.8607</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3868</v>
+        <v>1.5929</v>
       </c>
       <c r="E8" t="n">
-        <v>4.4177</v>
+        <v>4.9403</v>
       </c>
       <c r="F8" t="n">
         <v>2.9864</v>
@@ -818,16 +818,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.1156</v>
+        <v>4.4106</v>
       </c>
       <c r="C9" t="n">
-        <v>2.3832</v>
+        <v>2.554</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2493</v>
+        <v>1.3563</v>
       </c>
       <c r="E9" t="n">
-        <v>4.1156</v>
+        <v>4.4106</v>
       </c>
       <c r="F9" t="n">
         <v>2.4831</v>
@@ -864,16 +864,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.4004</v>
+        <v>3.6336</v>
       </c>
       <c r="C10" t="n">
-        <v>1.969</v>
+        <v>2.1041</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9237</v>
+        <v>1.0092</v>
       </c>
       <c r="E10" t="n">
-        <v>3.4004</v>
+        <v>3.6336</v>
       </c>
       <c r="F10" t="n">
         <v>2.5142</v>
@@ -906,403 +906,403 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>biguzera</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.3952</v>
+        <v>3.5683</v>
       </c>
       <c r="C11" t="n">
-        <v>1.966</v>
+        <v>2.0663</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9214</v>
+        <v>0.9801</v>
       </c>
       <c r="E11" t="n">
-        <v>3.3952</v>
+        <v>3.5683</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1994</v>
+        <v>3.303</v>
       </c>
       <c r="G11" t="n">
-        <v>2.1958</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1.1994</v>
+        <v>4.5044</v>
       </c>
       <c r="I11" t="n">
-        <v>1.1994</v>
+        <v>4.5044</v>
       </c>
       <c r="J11" t="n">
-        <v>2.1958</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>145</v>
+        <v>216</v>
       </c>
       <c r="L11" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3952</v>
+        <v>4.5044</v>
       </c>
       <c r="N11" t="n">
-        <v>240</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.3065</v>
+        <v>3.5205</v>
       </c>
       <c r="C12" t="n">
-        <v>1.9147</v>
+        <v>2.0386</v>
       </c>
       <c r="D12" t="n">
-        <v>0.881</v>
+        <v>0.9587</v>
       </c>
       <c r="E12" t="n">
-        <v>3.3065</v>
+        <v>3.5205</v>
       </c>
       <c r="F12" t="n">
-        <v>2.7064</v>
+        <v>2.7242</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6001</v>
+        <v>0.4745</v>
       </c>
       <c r="H12" t="n">
-        <v>3.1986</v>
+        <v>3.2375</v>
       </c>
       <c r="I12" t="n">
-        <v>3.1986</v>
+        <v>3.2375</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6001</v>
+        <v>0.4745</v>
       </c>
       <c r="K12" t="n">
-        <v>145</v>
+        <v>77</v>
       </c>
       <c r="L12" t="n">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="M12" t="n">
-        <v>3.7987</v>
+        <v>3.712</v>
       </c>
       <c r="N12" t="n">
-        <v>240</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.2556</v>
+        <v>3.4328</v>
       </c>
       <c r="C13" t="n">
-        <v>1.8852</v>
+        <v>1.9878</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8578</v>
+        <v>0.9195</v>
       </c>
       <c r="E13" t="n">
-        <v>3.2556</v>
+        <v>3.4328</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4797</v>
+        <v>2.7064</v>
       </c>
       <c r="G13" t="n">
-        <v>1.7759</v>
+        <v>0.6001</v>
       </c>
       <c r="H13" t="n">
-        <v>1.4797</v>
+        <v>3.1986</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5178</v>
+        <v>3.1986</v>
       </c>
       <c r="J13" t="n">
-        <v>1.7759</v>
+        <v>0.6001</v>
       </c>
       <c r="K13" t="n">
-        <v>200</v>
+        <v>145</v>
       </c>
       <c r="L13" t="n">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2937</v>
+        <v>3.7987</v>
       </c>
       <c r="N13" t="n">
-        <v>314</v>
+        <v>240</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>biguzera</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.2415</v>
+        <v>3.374</v>
       </c>
       <c r="C14" t="n">
-        <v>1.877</v>
+        <v>1.9537</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8514</v>
+        <v>0.8933</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2415</v>
+        <v>3.374</v>
       </c>
       <c r="F14" t="n">
-        <v>3.2415</v>
+        <v>1.1994</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2.1958</v>
       </c>
       <c r="H14" t="n">
-        <v>4.3696</v>
+        <v>1.1994</v>
       </c>
       <c r="I14" t="n">
-        <v>4.3696</v>
+        <v>1.1994</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>2.1958</v>
       </c>
       <c r="K14" t="n">
-        <v>216</v>
+        <v>145</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M14" t="n">
-        <v>4.3696</v>
+        <v>3.3952</v>
       </c>
       <c r="N14" t="n">
-        <v>216</v>
+        <v>240</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.1987</v>
+        <v>3.2662</v>
       </c>
       <c r="C15" t="n">
-        <v>1.8522</v>
+        <v>1.8913</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8319</v>
+        <v>0.8451</v>
       </c>
       <c r="E15" t="n">
-        <v>3.1987</v>
+        <v>3.2662</v>
       </c>
       <c r="F15" t="n">
-        <v>2.7242</v>
+        <v>1.4797</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4745</v>
+        <v>1.7759</v>
       </c>
       <c r="H15" t="n">
-        <v>3.2375</v>
+        <v>1.4797</v>
       </c>
       <c r="I15" t="n">
-        <v>3.2375</v>
+        <v>1.5178</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4745</v>
+        <v>1.7759</v>
       </c>
       <c r="K15" t="n">
-        <v>77</v>
+        <v>200</v>
       </c>
       <c r="L15" t="n">
-        <v>41</v>
+        <v>114</v>
       </c>
       <c r="M15" t="n">
-        <v>3.712</v>
+        <v>3.2937</v>
       </c>
       <c r="N15" t="n">
-        <v>118</v>
+        <v>314</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>Jimpphat</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.0738</v>
+        <v>3.2419</v>
       </c>
       <c r="C16" t="n">
-        <v>1.7799</v>
+        <v>1.8773</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7751</v>
+        <v>0.8343</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0738</v>
+        <v>3.2419</v>
       </c>
       <c r="F16" t="n">
-        <v>3.1465</v>
+        <v>3.2707</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0727</v>
+        <v>-0.2005</v>
       </c>
       <c r="H16" t="n">
-        <v>4.1617</v>
+        <v>4.4335</v>
       </c>
       <c r="I16" t="n">
-        <v>4.1617</v>
+        <v>4.4335</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.0727</v>
+        <v>-0.2005</v>
       </c>
       <c r="K16" t="n">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="L16" t="n">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="M16" t="n">
-        <v>4.089</v>
+        <v>4.233000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>191</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Jimpphat</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.0702</v>
+        <v>3.2165</v>
       </c>
       <c r="C17" t="n">
-        <v>1.7778</v>
+        <v>1.8625</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7734</v>
+        <v>0.8229</v>
       </c>
       <c r="E17" t="n">
-        <v>3.0702</v>
+        <v>3.2165</v>
       </c>
       <c r="F17" t="n">
-        <v>3.2707</v>
+        <v>3.1465</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2005</v>
+        <v>-0.0727</v>
       </c>
       <c r="H17" t="n">
-        <v>4.4335</v>
+        <v>4.1617</v>
       </c>
       <c r="I17" t="n">
-        <v>4.4335</v>
+        <v>4.1617</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.2005</v>
+        <v>-0.0727</v>
       </c>
       <c r="K17" t="n">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="L17" t="n">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="M17" t="n">
-        <v>4.233000000000001</v>
+        <v>4.089</v>
       </c>
       <c r="N17" t="n">
-        <v>118</v>
+        <v>191</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MAJ3R</t>
+          <t>Ax1Le</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.0647</v>
+        <v>3.1802</v>
       </c>
       <c r="C18" t="n">
-        <v>1.7746</v>
+        <v>1.8415</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7709</v>
+        <v>0.8067</v>
       </c>
       <c r="E18" t="n">
-        <v>3.0647</v>
+        <v>3.1802</v>
       </c>
       <c r="F18" t="n">
-        <v>3.2776</v>
+        <v>2.83</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2129</v>
+        <v>0.0249</v>
       </c>
       <c r="H18" t="n">
-        <v>4.4488</v>
+        <v>3.4691</v>
       </c>
       <c r="I18" t="n">
-        <v>4.4488</v>
+        <v>3.4691</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2129</v>
+        <v>0.0249</v>
       </c>
       <c r="K18" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="L18" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="M18" t="n">
-        <v>4.2359</v>
+        <v>3.494</v>
       </c>
       <c r="N18" t="n">
-        <v>170</v>
+        <v>158</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>MAJ3R</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.9396</v>
+        <v>3.1587</v>
       </c>
       <c r="C19" t="n">
-        <v>1.7022</v>
+        <v>1.8291</v>
       </c>
       <c r="D19" t="n">
-        <v>0.714</v>
+        <v>0.7971</v>
       </c>
       <c r="E19" t="n">
-        <v>2.9396</v>
+        <v>3.1587</v>
       </c>
       <c r="F19" t="n">
-        <v>3.3289</v>
+        <v>3.2776</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3893</v>
+        <v>-0.2129</v>
       </c>
       <c r="H19" t="n">
-        <v>4.5609</v>
+        <v>4.4488</v>
       </c>
       <c r="I19" t="n">
-        <v>4.5609</v>
+        <v>4.4488</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3893</v>
+        <v>-0.2129</v>
       </c>
       <c r="K19" t="n">
         <v>119</v>
@@ -1311,7 +1311,7 @@
         <v>51</v>
       </c>
       <c r="M19" t="n">
-        <v>4.1716</v>
+        <v>4.2359</v>
       </c>
       <c r="N19" t="n">
         <v>170</v>
@@ -1320,81 +1320,81 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>nexa</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.8843</v>
+        <v>3.0935</v>
       </c>
       <c r="C20" t="n">
-        <v>1.6702</v>
+        <v>1.7913</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6888</v>
+        <v>0.768</v>
       </c>
       <c r="E20" t="n">
-        <v>2.8843</v>
+        <v>3.0935</v>
       </c>
       <c r="F20" t="n">
-        <v>2.8283</v>
+        <v>3.3289</v>
       </c>
       <c r="G20" t="n">
-        <v>0.056</v>
+        <v>-0.3893</v>
       </c>
       <c r="H20" t="n">
-        <v>3.4654</v>
+        <v>4.5609</v>
       </c>
       <c r="I20" t="n">
-        <v>3.5547</v>
+        <v>4.5609</v>
       </c>
       <c r="J20" t="n">
-        <v>0.056</v>
+        <v>-0.3893</v>
       </c>
       <c r="K20" t="n">
-        <v>200</v>
+        <v>119</v>
       </c>
       <c r="L20" t="n">
-        <v>114</v>
+        <v>51</v>
       </c>
       <c r="M20" t="n">
-        <v>3.6107</v>
+        <v>4.1716</v>
       </c>
       <c r="N20" t="n">
-        <v>314</v>
+        <v>170</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ax1Le</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.8549</v>
+        <v>2.9419</v>
       </c>
       <c r="C21" t="n">
-        <v>1.6532</v>
+        <v>1.7035</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6754</v>
+        <v>0.7003</v>
       </c>
       <c r="E21" t="n">
-        <v>2.8549</v>
+        <v>2.9419</v>
       </c>
       <c r="F21" t="n">
-        <v>2.83</v>
+        <v>2.5376</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0249</v>
+        <v>0.2755</v>
       </c>
       <c r="H21" t="n">
-        <v>3.4691</v>
+        <v>2.8291</v>
       </c>
       <c r="I21" t="n">
-        <v>3.4691</v>
+        <v>2.8291</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0249</v>
+        <v>0.2755</v>
       </c>
       <c r="K21" t="n">
         <v>122</v>
@@ -1403,7 +1403,7 @@
         <v>36</v>
       </c>
       <c r="M21" t="n">
-        <v>3.494</v>
+        <v>3.1046</v>
       </c>
       <c r="N21" t="n">
         <v>158</v>
@@ -1412,185 +1412,185 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>Wicadia</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.8131</v>
+        <v>2.815</v>
       </c>
       <c r="C22" t="n">
-        <v>1.629</v>
+        <v>1.6301</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6564</v>
+        <v>0.6435999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>2.8131</v>
+        <v>2.815</v>
       </c>
       <c r="F22" t="n">
-        <v>2.5376</v>
+        <v>2.3019</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2755</v>
+        <v>0.3854</v>
       </c>
       <c r="H22" t="n">
-        <v>2.8291</v>
+        <v>2.3132</v>
       </c>
       <c r="I22" t="n">
-        <v>2.8291</v>
+        <v>2.3132</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2755</v>
+        <v>0.3854</v>
       </c>
       <c r="K22" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="L22" t="n">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="M22" t="n">
-        <v>3.1046</v>
+        <v>2.6986</v>
       </c>
       <c r="N22" t="n">
-        <v>158</v>
+        <v>170</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Wicadia</t>
+          <t>nexa</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.6873</v>
+        <v>2.7886</v>
       </c>
       <c r="C23" t="n">
-        <v>1.5561</v>
+        <v>1.6148</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5991</v>
+        <v>0.6318</v>
       </c>
       <c r="E23" t="n">
-        <v>2.6873</v>
+        <v>2.7886</v>
       </c>
       <c r="F23" t="n">
-        <v>2.3019</v>
+        <v>2.8283</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3854</v>
+        <v>0.056</v>
       </c>
       <c r="H23" t="n">
-        <v>2.3132</v>
+        <v>3.4654</v>
       </c>
       <c r="I23" t="n">
-        <v>2.3132</v>
+        <v>3.5547</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3854</v>
+        <v>0.056</v>
       </c>
       <c r="K23" t="n">
-        <v>119</v>
+        <v>200</v>
       </c>
       <c r="L23" t="n">
-        <v>51</v>
+        <v>114</v>
       </c>
       <c r="M23" t="n">
-        <v>2.6986</v>
+        <v>3.6107</v>
       </c>
       <c r="N23" t="n">
-        <v>170</v>
+        <v>314</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.6444</v>
+        <v>2.5842</v>
       </c>
       <c r="C24" t="n">
-        <v>1.5313</v>
+        <v>1.4964</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5796</v>
+        <v>0.5405</v>
       </c>
       <c r="E24" t="n">
-        <v>2.6444</v>
+        <v>2.5842</v>
       </c>
       <c r="F24" t="n">
-        <v>2.3342</v>
+        <v>2.4924</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3102</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2.384</v>
+        <v>2.7302</v>
       </c>
       <c r="I24" t="n">
-        <v>2.4454</v>
+        <v>2.7302</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3102</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>158</v>
+        <v>191</v>
       </c>
       <c r="L24" t="n">
-        <v>197</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>2.7556</v>
+        <v>2.7302</v>
       </c>
       <c r="N24" t="n">
-        <v>355</v>
+        <v>191</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.4924</v>
+        <v>2.58</v>
       </c>
       <c r="C25" t="n">
-        <v>1.4432</v>
+        <v>1.494</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5104</v>
+        <v>0.5386</v>
       </c>
       <c r="E25" t="n">
-        <v>2.4924</v>
+        <v>2.58</v>
       </c>
       <c r="F25" t="n">
-        <v>2.4924</v>
+        <v>2.3342</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>0.3102</v>
       </c>
       <c r="H25" t="n">
-        <v>2.7302</v>
+        <v>2.384</v>
       </c>
       <c r="I25" t="n">
-        <v>2.7302</v>
+        <v>2.4454</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>0.3102</v>
       </c>
       <c r="K25" t="n">
-        <v>191</v>
+        <v>158</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="M25" t="n">
-        <v>2.7302</v>
+        <v>2.7556</v>
       </c>
       <c r="N25" t="n">
-        <v>191</v>
+        <v>355</v>
       </c>
     </row>
     <row r="26">
@@ -1600,16 +1600,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.3737</v>
+        <v>2.4185</v>
       </c>
       <c r="C26" t="n">
-        <v>1.3745</v>
+        <v>1.4005</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4564</v>
+        <v>0.4665</v>
       </c>
       <c r="E26" t="n">
-        <v>2.3737</v>
+        <v>2.4185</v>
       </c>
       <c r="F26" t="n">
         <v>2.3737</v>
@@ -1642,231 +1642,231 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>Queenix</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.2361</v>
+        <v>2.2573</v>
       </c>
       <c r="C27" t="n">
-        <v>1.2948</v>
+        <v>1.3071</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3937</v>
+        <v>0.3945</v>
       </c>
       <c r="E27" t="n">
-        <v>2.2361</v>
+        <v>2.2573</v>
       </c>
       <c r="F27" t="n">
-        <v>2.5757</v>
+        <v>2.1403</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.3396</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>2.9124</v>
+        <v>2.1403</v>
       </c>
       <c r="I27" t="n">
-        <v>2.9124</v>
+        <v>2.1403</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.3396</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>106</v>
+        <v>175</v>
       </c>
       <c r="L27" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>2.5728</v>
+        <v>2.1403</v>
       </c>
       <c r="N27" t="n">
-        <v>191</v>
+        <v>175</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.1502</v>
+        <v>2.25</v>
       </c>
       <c r="C28" t="n">
-        <v>1.2451</v>
+        <v>1.3029</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3546</v>
+        <v>0.3912</v>
       </c>
       <c r="E28" t="n">
-        <v>2.1502</v>
+        <v>2.25</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7857</v>
+        <v>2.5757</v>
       </c>
       <c r="G28" t="n">
-        <v>1.3645</v>
+        <v>-0.3396</v>
       </c>
       <c r="H28" t="n">
-        <v>0.7857</v>
+        <v>2.9124</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8058999999999999</v>
+        <v>2.9124</v>
       </c>
       <c r="J28" t="n">
-        <v>1.3645</v>
+        <v>-0.3396</v>
       </c>
       <c r="K28" t="n">
-        <v>200</v>
+        <v>106</v>
       </c>
       <c r="L28" t="n">
-        <v>114</v>
+        <v>85</v>
       </c>
       <c r="M28" t="n">
-        <v>2.1704</v>
+        <v>2.5728</v>
       </c>
       <c r="N28" t="n">
-        <v>314</v>
+        <v>191</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Queenix</t>
+          <t>n1ssim</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.1403</v>
+        <v>2.0992</v>
       </c>
       <c r="C29" t="n">
-        <v>1.2394</v>
+        <v>1.2156</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3501</v>
+        <v>0.3238</v>
       </c>
       <c r="E29" t="n">
-        <v>2.1403</v>
+        <v>2.0992</v>
       </c>
       <c r="F29" t="n">
-        <v>2.1403</v>
+        <v>2.0247</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>2.1403</v>
+        <v>2.0247</v>
       </c>
       <c r="I29" t="n">
-        <v>2.1403</v>
+        <v>2.0247</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>175</v>
+        <v>216</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>2.1403</v>
+        <v>2.0247</v>
       </c>
       <c r="N29" t="n">
-        <v>175</v>
+        <v>216</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>n1ssim</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.0046</v>
+        <v>2.0978</v>
       </c>
       <c r="C30" t="n">
-        <v>1.1608</v>
+        <v>1.2148</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2883</v>
+        <v>0.3232</v>
       </c>
       <c r="E30" t="n">
-        <v>2.0046</v>
+        <v>2.0978</v>
       </c>
       <c r="F30" t="n">
-        <v>2.0046</v>
+        <v>0.7857</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1.3645</v>
       </c>
       <c r="H30" t="n">
-        <v>2.0046</v>
+        <v>0.7857</v>
       </c>
       <c r="I30" t="n">
-        <v>2.0046</v>
+        <v>0.8058999999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1.3645</v>
       </c>
       <c r="K30" t="n">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="M30" t="n">
-        <v>2.0046</v>
+        <v>2.1704</v>
       </c>
       <c r="N30" t="n">
-        <v>216</v>
+        <v>314</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.8825</v>
+        <v>1.9079</v>
       </c>
       <c r="C31" t="n">
-        <v>1.0901</v>
+        <v>1.1048</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2327</v>
+        <v>0.2384</v>
       </c>
       <c r="E31" t="n">
-        <v>1.8825</v>
+        <v>1.9079</v>
       </c>
       <c r="F31" t="n">
-        <v>2.3353</v>
+        <v>2.7428</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.4528</v>
+        <v>-1</v>
       </c>
       <c r="H31" t="n">
-        <v>2.3864</v>
+        <v>3.2782</v>
       </c>
       <c r="I31" t="n">
-        <v>2.3864</v>
+        <v>3.2782</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.4528</v>
+        <v>-1</v>
       </c>
       <c r="K31" t="n">
-        <v>122</v>
+        <v>77</v>
       </c>
       <c r="L31" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="M31" t="n">
-        <v>1.9336</v>
+        <v>2.2782</v>
       </c>
       <c r="N31" t="n">
-        <v>158</v>
+        <v>118</v>
       </c>
     </row>
     <row r="32">
@@ -1876,16 +1876,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.8178</v>
+        <v>1.8711</v>
       </c>
       <c r="C32" t="n">
-        <v>1.0526</v>
+        <v>1.0835</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2033</v>
+        <v>0.222</v>
       </c>
       <c r="E32" t="n">
-        <v>1.8178</v>
+        <v>1.8711</v>
       </c>
       <c r="F32" t="n">
         <v>1.8178</v>
@@ -1922,16 +1922,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.752</v>
+        <v>1.8683</v>
       </c>
       <c r="C33" t="n">
-        <v>1.0145</v>
+        <v>1.0819</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1733</v>
+        <v>0.2207</v>
       </c>
       <c r="E33" t="n">
-        <v>1.752</v>
+        <v>1.8683</v>
       </c>
       <c r="F33" t="n">
         <v>1.752</v>
@@ -1964,47 +1964,47 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.7428</v>
+        <v>1.8278</v>
       </c>
       <c r="C34" t="n">
-        <v>1.0092</v>
+        <v>1.0584</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1692</v>
+        <v>0.2026</v>
       </c>
       <c r="E34" t="n">
-        <v>1.7428</v>
+        <v>1.8278</v>
       </c>
       <c r="F34" t="n">
-        <v>2.7428</v>
+        <v>2.3353</v>
       </c>
       <c r="G34" t="n">
-        <v>-1</v>
+        <v>-0.4528</v>
       </c>
       <c r="H34" t="n">
-        <v>3.2782</v>
+        <v>2.3864</v>
       </c>
       <c r="I34" t="n">
-        <v>3.2782</v>
+        <v>2.3864</v>
       </c>
       <c r="J34" t="n">
-        <v>-1</v>
+        <v>-0.4528</v>
       </c>
       <c r="K34" t="n">
-        <v>77</v>
+        <v>122</v>
       </c>
       <c r="L34" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="M34" t="n">
-        <v>2.2782</v>
+        <v>1.9336</v>
       </c>
       <c r="N34" t="n">
-        <v>118</v>
+        <v>158</v>
       </c>
     </row>
     <row r="35">
@@ -2014,16 +2014,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.7366</v>
+        <v>1.5945</v>
       </c>
       <c r="C35" t="n">
-        <v>1.0056</v>
+        <v>0.9233</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1663</v>
+        <v>0.0984</v>
       </c>
       <c r="E35" t="n">
-        <v>1.7366</v>
+        <v>1.5945</v>
       </c>
       <c r="F35" t="n">
         <v>0.9186</v>
@@ -2056,185 +2056,185 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Nodios</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.613</v>
+        <v>1.5727</v>
       </c>
       <c r="C36" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.9107</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1101</v>
+        <v>0.0887</v>
       </c>
       <c r="E36" t="n">
-        <v>1.613</v>
+        <v>1.5727</v>
       </c>
       <c r="F36" t="n">
-        <v>1.613</v>
+        <v>1.4872</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1.613</v>
+        <v>1.4872</v>
       </c>
       <c r="I36" t="n">
-        <v>1.613</v>
+        <v>1.4872</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>175</v>
+        <v>119</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1.613</v>
+        <v>1.4872</v>
       </c>
       <c r="N36" t="n">
-        <v>175</v>
+        <v>119</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>lux</t>
+          <t>Boombl4</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.5489</v>
+        <v>1.5195</v>
       </c>
       <c r="C37" t="n">
-        <v>0.8969</v>
+        <v>0.8799</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0809</v>
+        <v>0.0649</v>
       </c>
       <c r="E37" t="n">
-        <v>1.5489</v>
+        <v>1.5195</v>
       </c>
       <c r="F37" t="n">
-        <v>1.5489</v>
+        <v>2.0606</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>-0.5750999999999999</v>
       </c>
       <c r="H37" t="n">
-        <v>1.5489</v>
+        <v>2.0606</v>
       </c>
       <c r="I37" t="n">
-        <v>1.5489</v>
+        <v>2.0606</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>-0.5750999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>216</v>
+        <v>122</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M37" t="n">
-        <v>1.5489</v>
+        <v>1.4855</v>
       </c>
       <c r="N37" t="n">
-        <v>216</v>
+        <v>158</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.5117</v>
+        <v>1.4925</v>
       </c>
       <c r="C38" t="n">
-        <v>0.8754</v>
+        <v>0.8642</v>
       </c>
       <c r="D38" t="n">
-        <v>0.064</v>
+        <v>0.0528</v>
       </c>
       <c r="E38" t="n">
-        <v>1.5117</v>
+        <v>1.4925</v>
       </c>
       <c r="F38" t="n">
-        <v>1.5117</v>
+        <v>1.3632</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1.5117</v>
+        <v>1.3632</v>
       </c>
       <c r="I38" t="n">
-        <v>1.5117</v>
+        <v>1.3632</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1.5117</v>
+        <v>1.3632</v>
       </c>
       <c r="N38" t="n">
-        <v>119</v>
+        <v>131</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Boombl4</t>
+          <t>lux</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.4855</v>
+        <v>1.4841</v>
       </c>
       <c r="C39" t="n">
-        <v>0.8602</v>
+        <v>0.8594000000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>0.052</v>
+        <v>0.0491</v>
       </c>
       <c r="E39" t="n">
-        <v>1.4855</v>
+        <v>1.4841</v>
       </c>
       <c r="F39" t="n">
-        <v>2.0606</v>
+        <v>1.5778</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.5750999999999999</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>2.0606</v>
+        <v>1.5778</v>
       </c>
       <c r="I39" t="n">
-        <v>2.0606</v>
+        <v>1.5778</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.5750999999999999</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>122</v>
+        <v>216</v>
       </c>
       <c r="L39" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>1.4855</v>
+        <v>1.5778</v>
       </c>
       <c r="N39" t="n">
-        <v>158</v>
+        <v>216</v>
       </c>
     </row>
     <row r="40">
@@ -2244,16 +2244,16 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.4759</v>
+        <v>1.404</v>
       </c>
       <c r="C40" t="n">
-        <v>0.8546</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0477</v>
+        <v>0.0133</v>
       </c>
       <c r="E40" t="n">
-        <v>1.4759</v>
+        <v>1.404</v>
       </c>
       <c r="F40" t="n">
         <v>2.2758</v>
@@ -2286,231 +2286,231 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>Nodios</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.3632</v>
+        <v>1.3079</v>
       </c>
       <c r="C41" t="n">
-        <v>0.7894</v>
+        <v>0.7574</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.0036</v>
+        <v>-0.0296</v>
       </c>
       <c r="E41" t="n">
-        <v>1.3632</v>
+        <v>1.3079</v>
       </c>
       <c r="F41" t="n">
-        <v>1.3632</v>
+        <v>1.613</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1.3632</v>
+        <v>1.613</v>
       </c>
       <c r="I41" t="n">
-        <v>1.3632</v>
+        <v>1.613</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>131</v>
+        <v>175</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1.3632</v>
+        <v>1.613</v>
       </c>
       <c r="N41" t="n">
-        <v>131</v>
+        <v>175</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>Patti</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.3088</v>
+        <v>1.1399</v>
       </c>
       <c r="C42" t="n">
-        <v>0.7579</v>
+        <v>0.6601</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.0284</v>
+        <v>-0.1047</v>
       </c>
       <c r="E42" t="n">
-        <v>1.3088</v>
+        <v>1.1399</v>
       </c>
       <c r="F42" t="n">
-        <v>1.2953</v>
+        <v>1.1015</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0135</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1.2953</v>
+        <v>1.1015</v>
       </c>
       <c r="I42" t="n">
-        <v>1.2953</v>
+        <v>1.1015</v>
       </c>
       <c r="J42" t="n">
-        <v>0.0135</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>106</v>
+        <v>175</v>
       </c>
       <c r="L42" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1.3088</v>
+        <v>1.1015</v>
       </c>
       <c r="N42" t="n">
-        <v>191</v>
+        <v>175</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Patti</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.1015</v>
+        <v>1.0439</v>
       </c>
       <c r="C43" t="n">
-        <v>0.6378</v>
+        <v>0.6045</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.1228</v>
+        <v>-0.1475</v>
       </c>
       <c r="E43" t="n">
-        <v>1.1015</v>
+        <v>1.0439</v>
       </c>
       <c r="F43" t="n">
-        <v>1.1015</v>
+        <v>1.2953</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>0.0135</v>
       </c>
       <c r="H43" t="n">
-        <v>1.1015</v>
+        <v>1.2953</v>
       </c>
       <c r="I43" t="n">
-        <v>1.1015</v>
+        <v>1.2953</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>0.0135</v>
       </c>
       <c r="K43" t="n">
-        <v>175</v>
+        <v>106</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M43" t="n">
-        <v>1.1015</v>
+        <v>1.3088</v>
       </c>
       <c r="N43" t="n">
-        <v>175</v>
+        <v>191</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>noway</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.0356</v>
+        <v>0.9996</v>
       </c>
       <c r="C44" t="n">
-        <v>0.5997</v>
+        <v>0.5788</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.1528</v>
+        <v>-0.1673</v>
       </c>
       <c r="E44" t="n">
-        <v>1.0356</v>
+        <v>0.9996</v>
       </c>
       <c r="F44" t="n">
-        <v>1.0356</v>
+        <v>0.1482</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>0.8445</v>
       </c>
       <c r="H44" t="n">
-        <v>1.0356</v>
+        <v>0.1482</v>
       </c>
       <c r="I44" t="n">
-        <v>1.0356</v>
+        <v>0.1482</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>0.8445</v>
       </c>
       <c r="K44" t="n">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M44" t="n">
-        <v>1.0356</v>
+        <v>0.9927</v>
       </c>
       <c r="N44" t="n">
-        <v>119</v>
+        <v>240</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>noway</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.9927</v>
+        <v>0.9084</v>
       </c>
       <c r="C45" t="n">
-        <v>0.5748</v>
+        <v>0.526</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.1723</v>
+        <v>-0.2081</v>
       </c>
       <c r="E45" t="n">
-        <v>0.9927</v>
+        <v>0.9084</v>
       </c>
       <c r="F45" t="n">
-        <v>0.1482</v>
+        <v>1.0356</v>
       </c>
       <c r="G45" t="n">
-        <v>0.8445</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1482</v>
+        <v>1.0356</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1482</v>
+        <v>1.0356</v>
       </c>
       <c r="J45" t="n">
-        <v>0.8445</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>145</v>
+        <v>119</v>
       </c>
       <c r="L45" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.9927</v>
+        <v>1.0356</v>
       </c>
       <c r="N45" t="n">
-        <v>240</v>
+        <v>119</v>
       </c>
     </row>
     <row r="46">
@@ -2520,16 +2520,16 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.971</v>
+        <v>0.8843</v>
       </c>
       <c r="C46" t="n">
-        <v>0.5623</v>
+        <v>0.5121</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.1822</v>
+        <v>-0.2188</v>
       </c>
       <c r="E46" t="n">
-        <v>0.971</v>
+        <v>0.8843</v>
       </c>
       <c r="F46" t="n">
         <v>0.971</v>
@@ -2562,446 +2562,446 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>decenty</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8346</v>
+        <v>0.8081</v>
       </c>
       <c r="C47" t="n">
-        <v>0.4833</v>
+        <v>0.4679</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.2443</v>
+        <v>-0.2529</v>
       </c>
       <c r="E47" t="n">
-        <v>0.8346</v>
+        <v>0.8081</v>
       </c>
       <c r="F47" t="n">
-        <v>0.8346</v>
+        <v>0.7697000000000001</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.8346</v>
+        <v>0.7697000000000001</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8346</v>
+        <v>0.7697000000000001</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>119</v>
+        <v>203</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.8346</v>
+        <v>0.7697000000000001</v>
       </c>
       <c r="N47" t="n">
-        <v>119</v>
+        <v>203</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>kraghen</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7697000000000001</v>
+        <v>0.8023</v>
       </c>
       <c r="C48" t="n">
-        <v>0.4457</v>
+        <v>0.4646</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.2738</v>
+        <v>-0.2555</v>
       </c>
       <c r="E48" t="n">
-        <v>0.7697000000000001</v>
+        <v>0.8023</v>
       </c>
       <c r="F48" t="n">
-        <v>0.7697000000000001</v>
+        <v>0.757</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.7697000000000001</v>
+        <v>0.757</v>
       </c>
       <c r="I48" t="n">
-        <v>0.7697000000000001</v>
+        <v>0.757</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>203</v>
+        <v>175</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.7697000000000001</v>
+        <v>0.757</v>
       </c>
       <c r="N48" t="n">
-        <v>203</v>
+        <v>175</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>decenty</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.76</v>
+        <v>0.7099</v>
       </c>
       <c r="C49" t="n">
-        <v>0.4401</v>
+        <v>0.4111</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.2782</v>
+        <v>-0.2967</v>
       </c>
       <c r="E49" t="n">
-        <v>0.76</v>
+        <v>0.7099</v>
       </c>
       <c r="F49" t="n">
-        <v>0.76</v>
+        <v>0.8346</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.76</v>
+        <v>0.8346</v>
       </c>
       <c r="I49" t="n">
-        <v>0.76</v>
+        <v>0.8346</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.76</v>
+        <v>0.8346</v>
       </c>
       <c r="N49" t="n">
-        <v>106</v>
+        <v>119</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>kraghen</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.757</v>
+        <v>0.6952</v>
       </c>
       <c r="C50" t="n">
-        <v>0.4383</v>
+        <v>0.4026</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.2796</v>
+        <v>-0.3033</v>
       </c>
       <c r="E50" t="n">
-        <v>0.757</v>
+        <v>0.6952</v>
       </c>
       <c r="F50" t="n">
-        <v>0.757</v>
+        <v>0.76</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.757</v>
+        <v>0.76</v>
       </c>
       <c r="I50" t="n">
-        <v>0.757</v>
+        <v>0.76</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>175</v>
+        <v>106</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.757</v>
+        <v>0.76</v>
       </c>
       <c r="N50" t="n">
-        <v>175</v>
+        <v>106</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6031</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="C51" t="n">
-        <v>0.3492</v>
+        <v>0.3546</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.3497</v>
+        <v>-0.3403</v>
       </c>
       <c r="E51" t="n">
-        <v>0.6031</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="F51" t="n">
-        <v>0.6031</v>
+        <v>0.5582</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.6031</v>
+        <v>0.5582</v>
       </c>
       <c r="I51" t="n">
-        <v>0.6031</v>
+        <v>0.5582</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>191</v>
+        <v>119</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.6031</v>
+        <v>0.5582</v>
       </c>
       <c r="N51" t="n">
-        <v>191</v>
+        <v>119</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5763</v>
+        <v>0.3925</v>
       </c>
       <c r="C52" t="n">
-        <v>0.3337</v>
+        <v>0.2273</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.3619</v>
+        <v>-0.4385</v>
       </c>
       <c r="E52" t="n">
-        <v>0.5763</v>
+        <v>0.3925</v>
       </c>
       <c r="F52" t="n">
-        <v>0.5763</v>
+        <v>0.6686</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>-0.1634</v>
       </c>
       <c r="H52" t="n">
-        <v>0.5763</v>
+        <v>0.6686</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5763</v>
+        <v>0.6686</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>-0.1634</v>
       </c>
       <c r="K52" t="n">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M52" t="n">
-        <v>0.5763</v>
+        <v>0.5052</v>
       </c>
       <c r="N52" t="n">
-        <v>119</v>
+        <v>191</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>VINI</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5052</v>
+        <v>0.3657</v>
       </c>
       <c r="C53" t="n">
-        <v>0.2925</v>
+        <v>0.2118</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.3942</v>
+        <v>-0.4505</v>
       </c>
       <c r="E53" t="n">
-        <v>0.5052</v>
+        <v>0.3657</v>
       </c>
       <c r="F53" t="n">
-        <v>0.6686</v>
+        <v>0.2942</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.1634</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.6686</v>
+        <v>0.2942</v>
       </c>
       <c r="I53" t="n">
-        <v>0.6686</v>
+        <v>0.2942</v>
       </c>
       <c r="J53" t="n">
-        <v>-0.1634</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="L53" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0.5052</v>
+        <v>0.2942</v>
       </c>
       <c r="N53" t="n">
-        <v>191</v>
+        <v>119</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.3193</v>
+        <v>0.3289</v>
       </c>
       <c r="C54" t="n">
-        <v>0.1849</v>
+        <v>0.1905</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4789</v>
+        <v>-0.4669</v>
       </c>
       <c r="E54" t="n">
-        <v>0.3193</v>
+        <v>0.3289</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.0152</v>
+        <v>0.6031</v>
       </c>
       <c r="G54" t="n">
-        <v>0.3345</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.0152</v>
+        <v>0.6031</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.0156</v>
+        <v>0.6031</v>
       </c>
       <c r="J54" t="n">
-        <v>0.3345</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>158</v>
+        <v>191</v>
       </c>
       <c r="L54" t="n">
-        <v>197</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.3189</v>
+        <v>0.6031</v>
       </c>
       <c r="N54" t="n">
-        <v>355</v>
+        <v>191</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.3022</v>
+        <v>0.274</v>
       </c>
       <c r="C55" t="n">
-        <v>0.175</v>
+        <v>0.1587</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.4866</v>
+        <v>-0.4914</v>
       </c>
       <c r="E55" t="n">
-        <v>0.3022</v>
+        <v>0.274</v>
       </c>
       <c r="F55" t="n">
-        <v>0.3177</v>
+        <v>0.2491</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.0155</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0.3177</v>
+        <v>0.2491</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3177</v>
+        <v>0.2491</v>
       </c>
       <c r="J55" t="n">
-        <v>-0.0155</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>119</v>
+        <v>203</v>
       </c>
       <c r="L55" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.3022</v>
+        <v>0.2491</v>
       </c>
       <c r="N55" t="n">
-        <v>170</v>
+        <v>203</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>VINI</t>
+          <t>nicoodoz</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.2942</v>
+        <v>0.2688</v>
       </c>
       <c r="C56" t="n">
-        <v>0.1704</v>
+        <v>0.1557</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.4903</v>
+        <v>-0.4938</v>
       </c>
       <c r="E56" t="n">
-        <v>0.2942</v>
+        <v>0.2688</v>
       </c>
       <c r="F56" t="n">
-        <v>0.2942</v>
+        <v>0.1799</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0.2942</v>
+        <v>0.1799</v>
       </c>
       <c r="I56" t="n">
-        <v>0.2942</v>
+        <v>0.1799</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -3013,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.2942</v>
+        <v>0.1799</v>
       </c>
       <c r="N56" t="n">
         <v>119</v>
@@ -3022,124 +3022,124 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.2491</v>
+        <v>0.2291</v>
       </c>
       <c r="C57" t="n">
-        <v>0.1442</v>
+        <v>0.1327</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5108</v>
+        <v>-0.5115</v>
       </c>
       <c r="E57" t="n">
-        <v>0.2491</v>
+        <v>0.2291</v>
       </c>
       <c r="F57" t="n">
-        <v>0.2491</v>
+        <v>-0.0152</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>0.3345</v>
       </c>
       <c r="H57" t="n">
-        <v>0.2491</v>
+        <v>-0.0152</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2491</v>
+        <v>-0.0156</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>0.3345</v>
       </c>
       <c r="K57" t="n">
-        <v>203</v>
+        <v>158</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="M57" t="n">
-        <v>0.2491</v>
+        <v>0.3189</v>
       </c>
       <c r="N57" t="n">
-        <v>203</v>
+        <v>355</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Calyx</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.2458</v>
+        <v>0.2118</v>
       </c>
       <c r="C58" t="n">
-        <v>0.1423</v>
+        <v>0.1226</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5123</v>
+        <v>-0.5192</v>
       </c>
       <c r="E58" t="n">
-        <v>0.2458</v>
+        <v>0.2118</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.5881</v>
+        <v>-0.0457</v>
       </c>
       <c r="G58" t="n">
-        <v>0.8339</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.5881</v>
+        <v>-0.0457</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.5881</v>
+        <v>-0.0457</v>
       </c>
       <c r="J58" t="n">
-        <v>0.8339</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="L58" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0.2458</v>
+        <v>-0.0457</v>
       </c>
       <c r="N58" t="n">
-        <v>170</v>
+        <v>106</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.2216</v>
+        <v>0.1872</v>
       </c>
       <c r="C59" t="n">
-        <v>0.1283</v>
+        <v>0.1084</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5233</v>
+        <v>-0.5302</v>
       </c>
       <c r="E59" t="n">
-        <v>0.2216</v>
+        <v>0.1872</v>
       </c>
       <c r="F59" t="n">
-        <v>0.2216</v>
+        <v>0.1918</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>0.2216</v>
+        <v>0.1918</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2216</v>
+        <v>0.1918</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>0.2216</v>
+        <v>0.1918</v>
       </c>
       <c r="N59" t="n">
         <v>131</v>
@@ -3160,216 +3160,216 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>Calyx</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.1918</v>
+        <v>0.1331</v>
       </c>
       <c r="C60" t="n">
-        <v>0.1111</v>
+        <v>0.0771</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5369</v>
+        <v>-0.5544</v>
       </c>
       <c r="E60" t="n">
-        <v>0.1918</v>
+        <v>0.1331</v>
       </c>
       <c r="F60" t="n">
-        <v>0.1918</v>
+        <v>-0.5881</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>0.8339</v>
       </c>
       <c r="H60" t="n">
-        <v>0.1918</v>
+        <v>-0.5881</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1918</v>
+        <v>-0.5881</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>0.8339</v>
       </c>
       <c r="K60" t="n">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M60" t="n">
-        <v>0.1918</v>
+        <v>0.2458</v>
       </c>
       <c r="N60" t="n">
-        <v>131</v>
+        <v>170</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>nicoodoz</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.179</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="C61" t="n">
-        <v>0.1037</v>
+        <v>0.0478</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.5427</v>
+        <v>-0.5769</v>
       </c>
       <c r="E61" t="n">
-        <v>0.179</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="F61" t="n">
-        <v>0.179</v>
+        <v>0.3177</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>-0.0155</v>
       </c>
       <c r="H61" t="n">
-        <v>0.179</v>
+        <v>0.3177</v>
       </c>
       <c r="I61" t="n">
-        <v>0.179</v>
+        <v>0.3177</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>-0.0155</v>
       </c>
       <c r="K61" t="n">
         <v>119</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M61" t="n">
-        <v>0.179</v>
+        <v>0.3022</v>
       </c>
       <c r="N61" t="n">
-        <v>119</v>
+        <v>170</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senzu</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.0793</v>
+        <v>0.0679</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0459</v>
+        <v>0.0393</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.5881</v>
+        <v>-0.5835</v>
       </c>
       <c r="E62" t="n">
-        <v>0.0793</v>
+        <v>0.0679</v>
       </c>
       <c r="F62" t="n">
-        <v>0.0793</v>
+        <v>0.0687</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>0.0793</v>
+        <v>0.0687</v>
       </c>
       <c r="I62" t="n">
-        <v>0.0793</v>
+        <v>0.0687</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>0.0793</v>
+        <v>0.0687</v>
       </c>
       <c r="N62" t="n">
-        <v>131</v>
+        <v>119</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.0687</v>
+        <v>0.026</v>
       </c>
       <c r="C63" t="n">
-        <v>0.0398</v>
+        <v>0.0151</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.5929</v>
+        <v>-0.6022</v>
       </c>
       <c r="E63" t="n">
-        <v>0.0687</v>
+        <v>0.026</v>
       </c>
       <c r="F63" t="n">
-        <v>0.0687</v>
+        <v>0.2216</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>0.0687</v>
+        <v>0.2216</v>
       </c>
       <c r="I63" t="n">
-        <v>0.0687</v>
+        <v>0.2216</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>0.0687</v>
+        <v>0.2216</v>
       </c>
       <c r="N63" t="n">
-        <v>119</v>
+        <v>131</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>Senzu</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.0314</v>
+        <v>0.0196</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.0182</v>
+        <v>0.0113</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.6385</v>
+        <v>-0.6051</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.0314</v>
+        <v>0.0196</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.0314</v>
+        <v>0.0793</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.0314</v>
+        <v>0.0793</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.0314</v>
+        <v>0.0793</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -3381,7 +3381,7 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.0314</v>
+        <v>0.0793</v>
       </c>
       <c r="N64" t="n">
         <v>131</v>
@@ -3390,185 +3390,185 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.0457</v>
+        <v>-0.0517</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.0265</v>
+        <v>-0.0299</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.645</v>
+        <v>-0.6369</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.0457</v>
+        <v>-0.0517</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.0457</v>
+        <v>-0.0314</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.0457</v>
+        <v>-0.0314</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.0457</v>
+        <v>-0.0314</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.0457</v>
+        <v>-0.0314</v>
       </c>
       <c r="N65" t="n">
-        <v>106</v>
+        <v>131</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>kauez</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.3446</v>
+        <v>-0.2326</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.1995</v>
+        <v>-0.1347</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7811</v>
+        <v>-0.7177</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.3446</v>
+        <v>-0.2326</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.3446</v>
+        <v>-0.5608</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.3446</v>
+        <v>-0.5608</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3446</v>
+        <v>-0.5608</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>216</v>
+        <v>106</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.3446</v>
+        <v>-0.5608</v>
       </c>
       <c r="N66" t="n">
-        <v>216</v>
+        <v>106</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>kauez</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.5448</v>
+        <v>-0.4413</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.3155</v>
+        <v>-0.2555</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8722</v>
+        <v>-0.8109</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.5448</v>
+        <v>-0.4413</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.5448</v>
+        <v>-0.2855</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.5448</v>
+        <v>-0.2855</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.5448</v>
+        <v>-0.2855</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>119</v>
+        <v>216</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.5448</v>
+        <v>-0.2855</v>
       </c>
       <c r="N67" t="n">
-        <v>119</v>
+        <v>216</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.5608</v>
+        <v>-0.8743</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.3247</v>
+        <v>-0.5063</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8794999999999999</v>
+        <v>-1.0044</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.5608</v>
+        <v>-0.8743</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.5608</v>
+        <v>-0.5445</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.5608</v>
+        <v>-0.5445</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.5608</v>
+        <v>-0.5445</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.5608</v>
+        <v>-0.5445</v>
       </c>
       <c r="N68" t="n">
-        <v>106</v>
+        <v>119</v>
       </c>
     </row>
     <row r="69">
@@ -3578,28 +3578,28 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.7592</v>
+        <v>-0.8978</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.4396</v>
+        <v>-0.5199</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.9698</v>
+        <v>-1.0148</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.7592</v>
+        <v>-0.8978</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.7592</v>
+        <v>-0.7589</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.7592</v>
+        <v>-0.7589</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.7592</v>
+        <v>-0.7589</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -3611,7 +3611,7 @@
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.7592</v>
+        <v>-0.7589</v>
       </c>
       <c r="N69" t="n">
         <v>119</v>
@@ -3620,139 +3620,139 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>arT</t>
+          <t>nqz</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.7641</v>
+        <v>-0.9273</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.4425</v>
+        <v>-0.537</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.972</v>
+        <v>-1.028</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.7641</v>
+        <v>-0.9273</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.7641</v>
+        <v>-0.8802</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.7641</v>
+        <v>-0.8802</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.7641</v>
+        <v>-0.8802</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>106</v>
+        <v>216</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.7641</v>
+        <v>-0.8802</v>
       </c>
       <c r="N70" t="n">
-        <v>106</v>
+        <v>216</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>nqz</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.8897</v>
+        <v>-0.9687</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.5152</v>
+        <v>-0.5609</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.0292</v>
+        <v>-1.0465</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.8897</v>
+        <v>-0.9687</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.8897</v>
+        <v>-0.9255</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.8897</v>
+        <v>-0.9255</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.8897</v>
+        <v>-0.9255</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>216</v>
+        <v>119</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.8897</v>
+        <v>-0.9255</v>
       </c>
       <c r="N71" t="n">
-        <v>216</v>
+        <v>119</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>arT</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.9255</v>
+        <v>-1.059</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.5359</v>
+        <v>-0.6132</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.0455</v>
+        <v>-1.0869</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.9255</v>
+        <v>-1.059</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.9255</v>
+        <v>-0.7641</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.9255</v>
+        <v>-0.7641</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.9255</v>
+        <v>-0.7641</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.9255</v>
+        <v>-0.7641</v>
       </c>
       <c r="N72" t="n">
-        <v>119</v>
+        <v>106</v>
       </c>
     </row>
     <row r="73">
@@ -3762,16 +3762,16 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.1512</v>
+        <v>-1.4717</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.6666</v>
+        <v>-0.8522</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.1483</v>
+        <v>-1.2712</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.1512</v>
+        <v>-1.4717</v>
       </c>
       <c r="F73" t="n">
         <v>-1.1512</v>
@@ -3808,16 +3808,16 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.4795</v>
+        <v>-1.7178</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.8567</v>
+        <v>-0.9947</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.2977</v>
+        <v>-1.3811</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.4795</v>
+        <v>-1.7178</v>
       </c>
       <c r="F74" t="n">
         <v>-1.4795</v>
@@ -3854,16 +3854,16 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.609</v>
+        <v>-1.7263</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.9317</v>
+        <v>-0.9996</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.3567</v>
+        <v>-1.3849</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.609</v>
+        <v>-1.7263</v>
       </c>
       <c r="F75" t="n">
         <v>-1.609</v>
@@ -3900,16 +3900,16 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.6738</v>
+        <v>-2.048</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.9692</v>
+        <v>-1.1859</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.3862</v>
+        <v>-1.5286</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.6738</v>
+        <v>-2.048</v>
       </c>
       <c r="F76" t="n">
         <v>-1.6738</v>
@@ -3946,16 +3946,16 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.7497</v>
+        <v>-2.0946</v>
       </c>
       <c r="C77" t="n">
-        <v>-1.0132</v>
+        <v>-1.2129</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.4207</v>
+        <v>-1.5494</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.7497</v>
+        <v>-2.0946</v>
       </c>
       <c r="F77" t="n">
         <v>-1.0898</v>
@@ -3992,16 +3992,16 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.834</v>
+        <v>-2.1112</v>
       </c>
       <c r="C78" t="n">
-        <v>-1.062</v>
+        <v>-1.2225</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.4591</v>
+        <v>-1.5568</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.834</v>
+        <v>-2.1112</v>
       </c>
       <c r="F78" t="n">
         <v>-1.7195</v>
@@ -4038,16 +4038,16 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-2.1242</v>
+        <v>-2.3612</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.23</v>
+        <v>-1.3673</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.5912</v>
+        <v>-1.6685</v>
       </c>
       <c r="E79" t="n">
-        <v>-2.1242</v>
+        <v>-2.3612</v>
       </c>
       <c r="F79" t="n">
         <v>-2.3365</v>
@@ -4080,35 +4080,35 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-4.0778</v>
+        <v>-4.4228</v>
       </c>
       <c r="C80" t="n">
-        <v>-2.3613</v>
+        <v>-2.5611</v>
       </c>
       <c r="D80" t="n">
-        <v>-2.4805</v>
+        <v>-2.5894</v>
       </c>
       <c r="E80" t="n">
-        <v>-4.0778</v>
+        <v>-4.4228</v>
       </c>
       <c r="F80" t="n">
-        <v>-2.3846</v>
+        <v>-3.1579</v>
       </c>
       <c r="G80" t="n">
-        <v>-1.6932</v>
+        <v>-1.1587</v>
       </c>
       <c r="H80" t="n">
-        <v>-2.3846</v>
+        <v>-3.1579</v>
       </c>
       <c r="I80" t="n">
-        <v>-2.5091</v>
+        <v>-3.3228</v>
       </c>
       <c r="J80" t="n">
-        <v>-1.6932</v>
+        <v>-1.1587</v>
       </c>
       <c r="K80" t="n">
         <v>227</v>
@@ -4117,7 +4117,7 @@
         <v>177</v>
       </c>
       <c r="M80" t="n">
-        <v>-4.2023</v>
+        <v>-4.4815</v>
       </c>
       <c r="N80" t="n">
         <v>404</v>
@@ -4126,35 +4126,35 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-4.3166</v>
+        <v>-4.4481</v>
       </c>
       <c r="C81" t="n">
-        <v>-2.4996</v>
+        <v>-2.5757</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.5892</v>
+        <v>-2.6007</v>
       </c>
       <c r="E81" t="n">
-        <v>-4.3166</v>
+        <v>-4.4481</v>
       </c>
       <c r="F81" t="n">
-        <v>-3.1579</v>
+        <v>-2.3846</v>
       </c>
       <c r="G81" t="n">
-        <v>-1.1587</v>
+        <v>-1.6932</v>
       </c>
       <c r="H81" t="n">
-        <v>-3.1579</v>
+        <v>-2.3846</v>
       </c>
       <c r="I81" t="n">
-        <v>-3.3228</v>
+        <v>-2.5091</v>
       </c>
       <c r="J81" t="n">
-        <v>-1.1587</v>
+        <v>-1.6932</v>
       </c>
       <c r="K81" t="n">
         <v>227</v>
@@ -4163,7 +4163,7 @@
         <v>177</v>
       </c>
       <c r="M81" t="n">
-        <v>-4.4815</v>
+        <v>-4.2023</v>
       </c>
       <c r="N81" t="n">
         <v>404</v>
@@ -15466,13 +15466,13 @@
         <v>19</v>
       </c>
       <c r="H282" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="I282" t="n">
-        <v>0.3356</v>
+        <v>0.3175</v>
       </c>
       <c r="J282" t="n">
-        <v>6.3764</v>
+        <v>6.0325</v>
       </c>
     </row>
     <row r="283">
@@ -15506,13 +15506,13 @@
         <v>19</v>
       </c>
       <c r="H283" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="I283" t="n">
-        <v>0.1446</v>
+        <v>0.1201</v>
       </c>
       <c r="J283" t="n">
-        <v>2.7474</v>
+        <v>2.2819</v>
       </c>
     </row>
     <row r="284">
@@ -15549,10 +15549,10 @@
         <v>1.02</v>
       </c>
       <c r="I284" t="n">
-        <v>0.0917</v>
+        <v>0.0926</v>
       </c>
       <c r="J284" t="n">
-        <v>1.7423</v>
+        <v>1.7594</v>
       </c>
     </row>
     <row r="285">
@@ -15589,10 +15589,10 @@
         <v>0.84</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.2022</v>
+        <v>-0.2019</v>
       </c>
       <c r="J285" t="n">
-        <v>-3.8418</v>
+        <v>-3.8361</v>
       </c>
     </row>
     <row r="286">
@@ -15629,10 +15629,10 @@
         <v>0.44</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.5653</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="J286" t="n">
-        <v>-10.7407</v>
+        <v>-10.735</v>
       </c>
     </row>
     <row r="287">
@@ -15666,13 +15666,13 @@
         <v>19</v>
       </c>
       <c r="H287" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="I287" t="n">
-        <v>1.5019</v>
+        <v>1.522</v>
       </c>
       <c r="J287" t="n">
-        <v>28.5361</v>
+        <v>28.918</v>
       </c>
     </row>
     <row r="288">
@@ -15706,13 +15706,13 @@
         <v>19</v>
       </c>
       <c r="H288" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I288" t="n">
-        <v>1.2212</v>
+        <v>1.2307</v>
       </c>
       <c r="J288" t="n">
-        <v>23.2028</v>
+        <v>23.3833</v>
       </c>
     </row>
     <row r="289">
@@ -15746,13 +15746,13 @@
         <v>19</v>
       </c>
       <c r="H289" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="I289" t="n">
-        <v>0.1239</v>
+        <v>0.183</v>
       </c>
       <c r="J289" t="n">
-        <v>2.3541</v>
+        <v>3.477</v>
       </c>
     </row>
     <row r="290">
@@ -15786,13 +15786,13 @@
         <v>19</v>
       </c>
       <c r="H290" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.0475</v>
+        <v>0.0873</v>
       </c>
       <c r="J290" t="n">
-        <v>-0.9025</v>
+        <v>1.6587</v>
       </c>
     </row>
     <row r="291">
@@ -15826,13 +15826,13 @@
         <v>19</v>
       </c>
       <c r="H291" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.2512</v>
+        <v>-0.2223</v>
       </c>
       <c r="J291" t="n">
-        <v>-4.7728</v>
+        <v>-4.2237</v>
       </c>
     </row>
     <row r="292">
